--- a/database/event/8027/event_8027_evp_summary.xlsx
+++ b/database/event/8027/event_8027_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>8.858599999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>1.5505</v>
       </c>
       <c r="D2" t="n">
         <v>3.1573</v>
@@ -545,7 +545,7 @@
         <v>4.3753</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.7658</v>
       </c>
       <c r="D3" t="n">
         <v>1.3462</v>
@@ -591,7 +591,7 @@
         <v>4.3249</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.757</v>
       </c>
       <c r="D4" t="n">
         <v>1.3258</v>
@@ -637,7 +637,7 @@
         <v>4.3197</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.7561</v>
       </c>
       <c r="D5" t="n">
         <v>1.3237</v>
@@ -683,7 +683,7 @@
         <v>4.2852</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="D6" t="n">
         <v>1.3098</v>
@@ -729,7 +729,7 @@
         <v>4.1843</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.7324000000000001</v>
       </c>
       <c r="D7" t="n">
         <v>1.269</v>
@@ -775,7 +775,7 @@
         <v>3.8635</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.6762</v>
       </c>
       <c r="D8" t="n">
         <v>1.1394</v>
@@ -821,7 +821,7 @@
         <v>3.6986</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.6474</v>
       </c>
       <c r="D9" t="n">
         <v>1.0728</v>
@@ -867,7 +867,7 @@
         <v>3.6753</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.6433</v>
       </c>
       <c r="D10" t="n">
         <v>1.0634</v>
@@ -913,7 +913,7 @@
         <v>3.6163</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.633</v>
       </c>
       <c r="D11" t="n">
         <v>1.0395</v>
@@ -959,7 +959,7 @@
         <v>3.5982</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.6298</v>
       </c>
       <c r="D12" t="n">
         <v>1.0322</v>
@@ -1005,7 +1005,7 @@
         <v>3.5882</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.628</v>
       </c>
       <c r="D13" t="n">
         <v>1.0282</v>
@@ -1051,7 +1051,7 @@
         <v>3.4526</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.6042999999999999</v>
       </c>
       <c r="D14" t="n">
         <v>0.9734</v>
@@ -1097,7 +1097,7 @@
         <v>3.3482</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="D15" t="n">
         <v>0.9312</v>
@@ -1143,7 +1143,7 @@
         <v>3.2952</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.5768</v>
       </c>
       <c r="D16" t="n">
         <v>0.9098000000000001</v>
@@ -1189,7 +1189,7 @@
         <v>3.2888</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.5756</v>
       </c>
       <c r="D17" t="n">
         <v>0.9072</v>
@@ -1235,7 +1235,7 @@
         <v>3.2163</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.5629</v>
       </c>
       <c r="D18" t="n">
         <v>0.878</v>
@@ -1281,7 +1281,7 @@
         <v>3.0956</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="D19" t="n">
         <v>0.8292</v>
@@ -1327,7 +1327,7 @@
         <v>3.0725</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="D20" t="n">
         <v>0.8199</v>
@@ -1373,7 +1373,7 @@
         <v>2.9493</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.5162</v>
       </c>
       <c r="D21" t="n">
         <v>0.7701</v>
@@ -1419,7 +1419,7 @@
         <v>2.5184</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.4408</v>
       </c>
       <c r="D22" t="n">
         <v>0.596</v>
@@ -1465,7 +1465,7 @@
         <v>2.5169</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.4405</v>
       </c>
       <c r="D23" t="n">
         <v>0.5954</v>
@@ -1511,7 +1511,7 @@
         <v>2.4438</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.4277</v>
       </c>
       <c r="D24" t="n">
         <v>0.5659</v>
@@ -1557,7 +1557,7 @@
         <v>2.1878</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.3829</v>
       </c>
       <c r="D25" t="n">
         <v>0.4625</v>
@@ -1603,7 +1603,7 @@
         <v>2.16</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.3781</v>
       </c>
       <c r="D26" t="n">
         <v>0.4512</v>
@@ -1649,7 +1649,7 @@
         <v>2.1197</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.371</v>
       </c>
       <c r="D27" t="n">
         <v>0.4349</v>
@@ -1695,7 +1695,7 @@
         <v>2.0991</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.3674</v>
       </c>
       <c r="D28" t="n">
         <v>0.4266</v>
@@ -1741,7 +1741,7 @@
         <v>2.0594</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.3605</v>
       </c>
       <c r="D29" t="n">
         <v>0.4106</v>
@@ -1787,7 +1787,7 @@
         <v>1.7809</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.3117</v>
       </c>
       <c r="D30" t="n">
         <v>0.2981</v>
@@ -1833,7 +1833,7 @@
         <v>1.659</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.2904</v>
       </c>
       <c r="D31" t="n">
         <v>0.2488</v>
@@ -1879,7 +1879,7 @@
         <v>1.6424</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.2875</v>
       </c>
       <c r="D32" t="n">
         <v>0.2421</v>
@@ -1925,7 +1925,7 @@
         <v>1.4397</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.252</v>
       </c>
       <c r="D33" t="n">
         <v>0.1602</v>
@@ -1971,7 +1971,7 @@
         <v>1.2792</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.2239</v>
       </c>
       <c r="D34" t="n">
         <v>0.0954</v>
@@ -2017,7 +2017,7 @@
         <v>1.2287</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2151</v>
       </c>
       <c r="D35" t="n">
         <v>0.075</v>
@@ -2063,7 +2063,7 @@
         <v>1.193</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2088</v>
       </c>
       <c r="D36" t="n">
         <v>0.0606</v>
@@ -2109,7 +2109,7 @@
         <v>0.9907</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.1734</v>
       </c>
       <c r="D37" t="n">
         <v>-0.0211</v>
@@ -2155,7 +2155,7 @@
         <v>0.723</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.1265</v>
       </c>
       <c r="D38" t="n">
         <v>-0.1293</v>
@@ -2201,7 +2201,7 @@
         <v>0.6142</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.1075</v>
       </c>
       <c r="D39" t="n">
         <v>-0.1732</v>
@@ -2247,7 +2247,7 @@
         <v>0.509</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.0891</v>
       </c>
       <c r="D40" t="n">
         <v>-0.2157</v>
@@ -2293,7 +2293,7 @@
         <v>0.423</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.074</v>
       </c>
       <c r="D41" t="n">
         <v>-0.2505</v>
@@ -2339,7 +2339,7 @@
         <v>0.3442</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.0602</v>
       </c>
       <c r="D42" t="n">
         <v>-0.2823</v>
@@ -2385,7 +2385,7 @@
         <v>0.3283</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.0575</v>
       </c>
       <c r="D43" t="n">
         <v>-0.2887</v>
@@ -2431,7 +2431,7 @@
         <v>0.2931</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.0513</v>
       </c>
       <c r="D44" t="n">
         <v>-0.303</v>
@@ -2477,7 +2477,7 @@
         <v>0.2408</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.0421</v>
       </c>
       <c r="D45" t="n">
         <v>-0.3241</v>
@@ -2523,7 +2523,7 @@
         <v>0.1652</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.0289</v>
       </c>
       <c r="D46" t="n">
         <v>-0.3546</v>
@@ -2569,7 +2569,7 @@
         <v>0.07920000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.0139</v>
       </c>
       <c r="D47" t="n">
         <v>-0.3894</v>
@@ -2615,7 +2615,7 @@
         <v>0.051</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.0089</v>
       </c>
       <c r="D48" t="n">
         <v>-0.4008</v>
@@ -2661,7 +2661,7 @@
         <v>-0.0711</v>
       </c>
       <c r="C49" t="n">
-        <v>-0</v>
+        <v>-0.0124</v>
       </c>
       <c r="D49" t="n">
         <v>-0.4501</v>
@@ -2707,7 +2707,7 @@
         <v>-0.2153</v>
       </c>
       <c r="C50" t="n">
-        <v>-0</v>
+        <v>-0.0377</v>
       </c>
       <c r="D50" t="n">
         <v>-0.5083</v>
@@ -2753,7 +2753,7 @@
         <v>-0.2192</v>
       </c>
       <c r="C51" t="n">
-        <v>-0</v>
+        <v>-0.0384</v>
       </c>
       <c r="D51" t="n">
         <v>-0.5099</v>
@@ -2799,7 +2799,7 @@
         <v>-0.254</v>
       </c>
       <c r="C52" t="n">
-        <v>-0</v>
+        <v>-0.0445</v>
       </c>
       <c r="D52" t="n">
         <v>-0.524</v>
@@ -2845,7 +2845,7 @@
         <v>-0.3063</v>
       </c>
       <c r="C53" t="n">
-        <v>-0</v>
+        <v>-0.0536</v>
       </c>
       <c r="D53" t="n">
         <v>-0.5451</v>
@@ -2891,7 +2891,7 @@
         <v>-0.337</v>
       </c>
       <c r="C54" t="n">
-        <v>-0</v>
+        <v>-0.059</v>
       </c>
       <c r="D54" t="n">
         <v>-0.5575</v>
@@ -2937,7 +2937,7 @@
         <v>-0.3879</v>
       </c>
       <c r="C55" t="n">
-        <v>-0</v>
+        <v>-0.0679</v>
       </c>
       <c r="D55" t="n">
         <v>-0.5780999999999999</v>
@@ -2983,7 +2983,7 @@
         <v>-0.4004</v>
       </c>
       <c r="C56" t="n">
-        <v>-0</v>
+        <v>-0.0701</v>
       </c>
       <c r="D56" t="n">
         <v>-0.5831</v>
@@ -3029,7 +3029,7 @@
         <v>-0.4469</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D57" t="n">
         <v>-0.6019</v>
@@ -3075,7 +3075,7 @@
         <v>-0.5542</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.097</v>
       </c>
       <c r="D58" t="n">
         <v>-0.6452</v>
@@ -3121,7 +3121,7 @@
         <v>-0.6002999999999999</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1051</v>
       </c>
       <c r="D59" t="n">
         <v>-0.6639</v>
@@ -3167,7 +3167,7 @@
         <v>-0.6683</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.117</v>
       </c>
       <c r="D60" t="n">
         <v>-0.6913</v>
@@ -3213,7 +3213,7 @@
         <v>-0.6820000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.1194</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6969</v>
@@ -3259,7 +3259,7 @@
         <v>-0.7516</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.1316</v>
       </c>
       <c r="D62" t="n">
         <v>-0.725</v>
@@ -3305,7 +3305,7 @@
         <v>-0.799</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.1398</v>
       </c>
       <c r="D63" t="n">
         <v>-0.7441</v>
@@ -3351,7 +3351,7 @@
         <v>-0.8424</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.1474</v>
       </c>
       <c r="D64" t="n">
         <v>-0.7617</v>
@@ -3397,7 +3397,7 @@
         <v>-0.8457</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.148</v>
       </c>
       <c r="D65" t="n">
         <v>-0.763</v>
@@ -3443,7 +3443,7 @@
         <v>-0.8657</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.1515</v>
       </c>
       <c r="D66" t="n">
         <v>-0.7711</v>
@@ -3489,7 +3489,7 @@
         <v>-0.8732</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.1528</v>
       </c>
       <c r="D67" t="n">
         <v>-0.7741</v>
@@ -3535,7 +3535,7 @@
         <v>-0.9454</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.1655</v>
       </c>
       <c r="D68" t="n">
         <v>-0.8033</v>
@@ -3581,7 +3581,7 @@
         <v>-0.9573</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.1676</v>
       </c>
       <c r="D69" t="n">
         <v>-0.8081</v>
@@ -3627,7 +3627,7 @@
         <v>-0.9905</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.1734</v>
       </c>
       <c r="D70" t="n">
         <v>-0.8215</v>
@@ -3673,7 +3673,7 @@
         <v>-1.0962</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.1919</v>
       </c>
       <c r="D71" t="n">
         <v>-0.8642</v>
@@ -3719,7 +3719,7 @@
         <v>-1.1593</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.2029</v>
       </c>
       <c r="D72" t="n">
         <v>-0.8897</v>
@@ -3765,7 +3765,7 @@
         <v>-1.163</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.2036</v>
       </c>
       <c r="D73" t="n">
         <v>-0.8912</v>
@@ -3811,7 +3811,7 @@
         <v>-1.1747</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.2056</v>
       </c>
       <c r="D74" t="n">
         <v>-0.8959</v>
@@ -3857,7 +3857,7 @@
         <v>-1.2165</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-0.2129</v>
       </c>
       <c r="D75" t="n">
         <v>-0.9127999999999999</v>
@@ -3903,7 +3903,7 @@
         <v>-1.2215</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-0.2138</v>
       </c>
       <c r="D76" t="n">
         <v>-0.9147999999999999</v>
@@ -3949,7 +3949,7 @@
         <v>-1.3119</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-0.2296</v>
       </c>
       <c r="D77" t="n">
         <v>-0.9513</v>
@@ -3995,7 +3995,7 @@
         <v>-1.8882</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-0.3305</v>
       </c>
       <c r="D78" t="n">
         <v>-1.1842</v>
@@ -4041,7 +4041,7 @@
         <v>-1.9787</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-0.3463</v>
       </c>
       <c r="D79" t="n">
         <v>-1.2207</v>
@@ -4087,7 +4087,7 @@
         <v>-2.256</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-0.3949</v>
       </c>
       <c r="D80" t="n">
         <v>-1.3327</v>
@@ -4133,7 +4133,7 @@
         <v>-3.0758</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-0.5384</v>
       </c>
       <c r="D81" t="n">
         <v>-1.6639</v>

--- a/database/event/8027/event_8027_evp_summary.xlsx
+++ b/database/event/8027/event_8027_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.858599999999999</v>
+        <v>9.789400000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1.5505</v>
+        <v>1.7134</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1573</v>
+        <v>3.4562</v>
       </c>
       <c r="E2" t="n">
-        <v>8.858599999999999</v>
+        <v>9.789400000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8136</v>
+        <v>3.7444</v>
       </c>
       <c r="G2" t="n">
         <v>6.045</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8136</v>
+        <v>3.7444</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8136</v>
+        <v>3.7444</v>
       </c>
       <c r="J2" t="n">
         <v>6.045</v>
@@ -529,7 +529,7 @@
         <v>235</v>
       </c>
       <c r="M2" t="n">
-        <v>8.858599999999999</v>
+        <v>9.789400000000001</v>
       </c>
       <c r="N2" t="n">
         <v>372</v>
@@ -538,124 +538,124 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.3753</v>
+        <v>4.7373</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7658</v>
+        <v>0.8292</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3462</v>
+        <v>1.4434</v>
       </c>
       <c r="E3" t="n">
-        <v>4.3753</v>
+        <v>4.7373</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7079</v>
+        <v>2.8265</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6674</v>
+        <v>1.9108</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7079</v>
+        <v>2.8265</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7079</v>
+        <v>2.8743</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6674</v>
+        <v>1.9108</v>
       </c>
       <c r="K3" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="L3" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M3" t="n">
-        <v>4.3753</v>
+        <v>4.7851</v>
       </c>
       <c r="N3" t="n">
-        <v>372</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.3249</v>
+        <v>4.3753</v>
       </c>
       <c r="C4" t="n">
-        <v>0.757</v>
+        <v>0.7658</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3258</v>
+        <v>1.2992</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3249</v>
+        <v>4.3753</v>
       </c>
       <c r="F4" t="n">
-        <v>4.3249</v>
+        <v>1.7079</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>2.6674</v>
       </c>
       <c r="H4" t="n">
-        <v>4.4784</v>
+        <v>1.7079</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4993</v>
+        <v>1.7079</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2.6674</v>
       </c>
       <c r="K4" t="n">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="M4" t="n">
-        <v>4.4993</v>
+        <v>4.3753</v>
       </c>
       <c r="N4" t="n">
-        <v>238</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3197</v>
+        <v>4.3143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7561</v>
+        <v>0.7551</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3237</v>
+        <v>1.2749</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3197</v>
+        <v>4.3143</v>
       </c>
       <c r="F5" t="n">
-        <v>4.3197</v>
+        <v>4.3143</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4703</v>
+        <v>4.4617</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4911</v>
+        <v>4.4993</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4911</v>
+        <v>4.4993</v>
       </c>
       <c r="N5" t="n">
         <v>238</v>
@@ -676,47 +676,47 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.2852</v>
+        <v>4.3091</v>
       </c>
       <c r="C6" t="n">
-        <v>0.75</v>
+        <v>0.7542</v>
       </c>
       <c r="D6" t="n">
-        <v>1.3098</v>
+        <v>1.2728</v>
       </c>
       <c r="E6" t="n">
-        <v>4.2852</v>
+        <v>4.3091</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3744</v>
+        <v>4.3091</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9108</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3744</v>
+        <v>4.4536</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3965</v>
+        <v>4.4911</v>
       </c>
       <c r="J6" t="n">
-        <v>1.9108</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="L6" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>4.3073</v>
+        <v>4.4911</v>
       </c>
       <c r="N6" t="n">
-        <v>416</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7">
@@ -732,7 +732,7 @@
         <v>0.7324000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>1.269</v>
+        <v>1.2231</v>
       </c>
       <c r="E7" t="n">
         <v>4.1843</v>
@@ -768,81 +768,81 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.8635</v>
+        <v>3.9877</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6762</v>
+        <v>0.698</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1394</v>
+        <v>1.1448</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8635</v>
+        <v>3.9877</v>
       </c>
       <c r="F8" t="n">
-        <v>3.7022</v>
+        <v>2.6939</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1613</v>
+        <v>1.2938</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7022</v>
+        <v>2.6939</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0007</v>
+        <v>2.7394</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1613</v>
+        <v>1.2938</v>
       </c>
       <c r="K8" t="n">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="L8" t="n">
-        <v>64</v>
+        <v>227</v>
       </c>
       <c r="M8" t="n">
-        <v>3.162</v>
+        <v>4.0332</v>
       </c>
       <c r="N8" t="n">
-        <v>219</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>siuhy</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.6986</v>
+        <v>3.8635</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6474</v>
+        <v>0.6762</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0728</v>
+        <v>1.0953</v>
       </c>
       <c r="E9" t="n">
-        <v>3.6986</v>
+        <v>3.8635</v>
       </c>
       <c r="F9" t="n">
-        <v>3.8227</v>
+        <v>3.7022</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1241</v>
+        <v>0.1613</v>
       </c>
       <c r="H9" t="n">
-        <v>3.8227</v>
+        <v>3.7022</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0984</v>
+        <v>3.0007</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.1241</v>
+        <v>0.1613</v>
       </c>
       <c r="K9" t="n">
         <v>155</v>
@@ -851,7 +851,7 @@
         <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>2.9743</v>
+        <v>3.162</v>
       </c>
       <c r="N9" t="n">
         <v>219</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>siuhy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.6753</v>
+        <v>3.6986</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6433</v>
+        <v>0.6474</v>
       </c>
       <c r="D10" t="n">
-        <v>1.0634</v>
+        <v>1.0296</v>
       </c>
       <c r="E10" t="n">
-        <v>3.6753</v>
+        <v>3.6986</v>
       </c>
       <c r="F10" t="n">
-        <v>4.3382</v>
+        <v>3.8227</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6629</v>
+        <v>-0.1241</v>
       </c>
       <c r="H10" t="n">
-        <v>4.8933</v>
+        <v>3.8227</v>
       </c>
       <c r="I10" t="n">
-        <v>3.9661</v>
+        <v>3.0984</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6629</v>
+        <v>-0.1241</v>
       </c>
       <c r="K10" t="n">
         <v>155</v>
@@ -897,7 +897,7 @@
         <v>64</v>
       </c>
       <c r="M10" t="n">
-        <v>3.3032</v>
+        <v>2.9743</v>
       </c>
       <c r="N10" t="n">
         <v>219</v>
@@ -906,553 +906,553 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.6163</v>
+        <v>3.6753</v>
       </c>
       <c r="C11" t="n">
-        <v>0.633</v>
+        <v>0.6433</v>
       </c>
       <c r="D11" t="n">
-        <v>1.0395</v>
+        <v>1.0203</v>
       </c>
       <c r="E11" t="n">
-        <v>3.6163</v>
+        <v>3.6753</v>
       </c>
       <c r="F11" t="n">
-        <v>2.371</v>
+        <v>4.3382</v>
       </c>
       <c r="G11" t="n">
-        <v>1.2453</v>
+        <v>-0.6629</v>
       </c>
       <c r="H11" t="n">
-        <v>2.371</v>
+        <v>4.8933</v>
       </c>
       <c r="I11" t="n">
-        <v>2.3931</v>
+        <v>3.9661</v>
       </c>
       <c r="J11" t="n">
-        <v>1.2453</v>
+        <v>-0.6629</v>
       </c>
       <c r="K11" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="L11" t="n">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6384</v>
+        <v>3.3032</v>
       </c>
       <c r="N11" t="n">
-        <v>416</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.5982</v>
+        <v>3.5986</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6298</v>
+        <v>0.6299</v>
       </c>
       <c r="D12" t="n">
-        <v>1.0322</v>
+        <v>0.9898</v>
       </c>
       <c r="E12" t="n">
-        <v>3.5982</v>
+        <v>3.5986</v>
       </c>
       <c r="F12" t="n">
-        <v>4.4134</v>
+        <v>2.3533</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.8152</v>
+        <v>1.2453</v>
       </c>
       <c r="H12" t="n">
-        <v>5.1956</v>
+        <v>2.3533</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2111</v>
+        <v>2.3931</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.8152</v>
+        <v>1.2453</v>
       </c>
       <c r="K12" t="n">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="L12" t="n">
-        <v>55</v>
+        <v>227</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3959</v>
+        <v>3.6384</v>
       </c>
       <c r="N12" t="n">
-        <v>229</v>
+        <v>416</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.5882</v>
+        <v>3.5982</v>
       </c>
       <c r="C13" t="n">
-        <v>0.628</v>
+        <v>0.6298</v>
       </c>
       <c r="D13" t="n">
-        <v>1.0282</v>
+        <v>0.9896</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5882</v>
+        <v>3.5982</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2944</v>
+        <v>4.4134</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2938</v>
+        <v>-0.8152</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2944</v>
+        <v>5.1956</v>
       </c>
       <c r="I13" t="n">
-        <v>2.3158</v>
+        <v>4.2111</v>
       </c>
       <c r="J13" t="n">
-        <v>1.2938</v>
+        <v>-0.8152</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="L13" t="n">
-        <v>227</v>
+        <v>55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6096</v>
+        <v>3.3959</v>
       </c>
       <c r="N13" t="n">
-        <v>416</v>
+        <v>229</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Perfecto</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.4526</v>
+        <v>3.5201</v>
       </c>
       <c r="C14" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.6161</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9734</v>
+        <v>0.9585</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4526</v>
+        <v>3.5201</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4526</v>
+        <v>3.4765</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4526</v>
+        <v>3.4765</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4687</v>
+        <v>3.5057</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.0436</v>
       </c>
       <c r="K14" t="n">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M14" t="n">
-        <v>3.4687</v>
+        <v>3.5493</v>
       </c>
       <c r="N14" t="n">
-        <v>164</v>
+        <v>260</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>Perfecto</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.3482</v>
+        <v>3.4397</v>
       </c>
       <c r="C15" t="n">
-        <v>0.586</v>
+        <v>0.6021</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9312</v>
+        <v>0.9265</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3482</v>
+        <v>3.4397</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1096</v>
+        <v>3.4397</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2386</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1096</v>
+        <v>3.4397</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1195</v>
+        <v>3.4687</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2386</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="L15" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3581</v>
+        <v>3.4687</v>
       </c>
       <c r="N15" t="n">
-        <v>260</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.2952</v>
+        <v>3.3404</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5768</v>
+        <v>0.5847</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9098000000000001</v>
+        <v>0.8869</v>
       </c>
       <c r="E16" t="n">
-        <v>3.2952</v>
+        <v>3.3404</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1049</v>
+        <v>2.1018</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1903</v>
+        <v>1.2386</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1049</v>
+        <v>2.1018</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8955</v>
+        <v>2.1195</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1903</v>
+        <v>1.2386</v>
       </c>
       <c r="K16" t="n">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="M16" t="n">
-        <v>3.0858</v>
+        <v>3.3581</v>
       </c>
       <c r="N16" t="n">
-        <v>229</v>
+        <v>260</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.2888</v>
+        <v>3.3081</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5756</v>
+        <v>0.579</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9072</v>
+        <v>0.874</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2888</v>
+        <v>3.3081</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9683</v>
+        <v>1.1177</v>
       </c>
       <c r="G17" t="n">
-        <v>2.3205</v>
+        <v>2.1903</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9683</v>
+        <v>1.1177</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9772999999999999</v>
+        <v>0.906</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3205</v>
+        <v>2.1903</v>
       </c>
       <c r="K17" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="L17" t="n">
-        <v>227</v>
+        <v>55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2978</v>
+        <v>3.0963</v>
       </c>
       <c r="N17" t="n">
-        <v>416</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jambo</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2163</v>
+        <v>3.2816</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5629</v>
+        <v>0.5744</v>
       </c>
       <c r="D18" t="n">
-        <v>0.878</v>
+        <v>0.8635</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2163</v>
+        <v>3.2816</v>
       </c>
       <c r="F18" t="n">
-        <v>2.7753</v>
+        <v>0.9611</v>
       </c>
       <c r="G18" t="n">
-        <v>0.441</v>
+        <v>2.3205</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7753</v>
+        <v>0.9611</v>
       </c>
       <c r="I18" t="n">
-        <v>2.7753</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.441</v>
+        <v>2.3205</v>
       </c>
       <c r="K18" t="n">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="L18" t="n">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2163</v>
+        <v>3.2978</v>
       </c>
       <c r="N18" t="n">
-        <v>205</v>
+        <v>416</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>jambo</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0956</v>
+        <v>3.2669</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5417999999999999</v>
+        <v>0.5718</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8292</v>
+        <v>0.8576</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0956</v>
+        <v>3.2669</v>
       </c>
       <c r="F19" t="n">
-        <v>3.0956</v>
+        <v>2.8259</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0956</v>
+        <v>2.8259</v>
       </c>
       <c r="I19" t="n">
-        <v>3.11</v>
+        <v>2.8259</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.441</v>
       </c>
       <c r="K19" t="n">
-        <v>238</v>
+        <v>145</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M19" t="n">
-        <v>3.11</v>
+        <v>3.2669</v>
       </c>
       <c r="N19" t="n">
-        <v>238</v>
+        <v>205</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.0725</v>
+        <v>3.084</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8199</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>3.0725</v>
+        <v>3.084</v>
       </c>
       <c r="F20" t="n">
-        <v>3.2971</v>
+        <v>3.084</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2246</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2971</v>
+        <v>3.084</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6724</v>
+        <v>3.11</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2246</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>2.4478</v>
+        <v>3.11</v>
       </c>
       <c r="N20" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9493</v>
+        <v>3.0725</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5162</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7701</v>
+        <v>0.7802</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9493</v>
+        <v>3.0725</v>
       </c>
       <c r="F21" t="n">
-        <v>2.9057</v>
+        <v>3.2971</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0436</v>
+        <v>-0.2246</v>
       </c>
       <c r="H21" t="n">
-        <v>2.9057</v>
+        <v>3.2971</v>
       </c>
       <c r="I21" t="n">
-        <v>2.9193</v>
+        <v>2.6724</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0436</v>
+        <v>-0.2246</v>
       </c>
       <c r="K21" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9629</v>
+        <v>2.4478</v>
       </c>
       <c r="N21" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.5184</v>
+        <v>2.8353</v>
       </c>
       <c r="C22" t="n">
-        <v>0.4408</v>
+        <v>0.4963</v>
       </c>
       <c r="D22" t="n">
-        <v>0.596</v>
+        <v>0.6857</v>
       </c>
       <c r="E22" t="n">
-        <v>2.5184</v>
+        <v>2.8353</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5184</v>
+        <v>2.8353</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>2.5184</v>
+        <v>2.8353</v>
       </c>
       <c r="I22" t="n">
-        <v>2.5301</v>
+        <v>2.8353</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.5301</v>
+        <v>2.8353</v>
       </c>
       <c r="N22" t="n">
-        <v>164</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>0.4405</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5954</v>
+        <v>0.5588</v>
       </c>
       <c r="E23" t="n">
         <v>2.5169</v>
@@ -1504,173 +1504,173 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.4438</v>
+        <v>2.509</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4277</v>
+        <v>0.4391</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5659</v>
+        <v>0.5557</v>
       </c>
       <c r="E24" t="n">
-        <v>2.4438</v>
+        <v>2.509</v>
       </c>
       <c r="F24" t="n">
-        <v>2.4438</v>
+        <v>2.509</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2.4438</v>
+        <v>2.509</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4438</v>
+        <v>2.5301</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>2.4438</v>
+        <v>2.5301</v>
       </c>
       <c r="N24" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="C25" t="n">
-        <v>0.3829</v>
+        <v>0.4052</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4625</v>
+        <v>0.4785</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="I25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.1878</v>
+        <v>2.3153</v>
       </c>
       <c r="N25" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.16</v>
+        <v>2.1878</v>
       </c>
       <c r="C26" t="n">
-        <v>0.3781</v>
+        <v>0.3829</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4512</v>
+        <v>0.4277</v>
       </c>
       <c r="E26" t="n">
-        <v>2.16</v>
+        <v>2.1878</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.3163</v>
+        <v>2.1878</v>
       </c>
       <c r="G26" t="n">
-        <v>2.4763</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.3163</v>
+        <v>2.1878</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3163</v>
+        <v>2.1878</v>
       </c>
       <c r="J26" t="n">
-        <v>2.4763</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L26" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.16</v>
+        <v>2.1878</v>
       </c>
       <c r="N26" t="n">
-        <v>372</v>
+        <v>130</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.1197</v>
+        <v>2.16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.371</v>
+        <v>0.3781</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4349</v>
+        <v>0.4166</v>
       </c>
       <c r="E27" t="n">
-        <v>2.1197</v>
+        <v>2.16</v>
       </c>
       <c r="F27" t="n">
-        <v>1.7925</v>
+        <v>-0.3163</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3272</v>
+        <v>2.4763</v>
       </c>
       <c r="H27" t="n">
-        <v>1.7925</v>
+        <v>-0.3163</v>
       </c>
       <c r="I27" t="n">
-        <v>1.7925</v>
+        <v>-0.3163</v>
       </c>
       <c r="J27" t="n">
-        <v>0.3272</v>
+        <v>2.4763</v>
       </c>
       <c r="K27" t="n">
         <v>137</v>
@@ -1679,7 +1679,7 @@
         <v>235</v>
       </c>
       <c r="M27" t="n">
-        <v>2.1197</v>
+        <v>2.16</v>
       </c>
       <c r="N27" t="n">
         <v>372</v>
@@ -1688,354 +1688,354 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.0991</v>
+        <v>2.1197</v>
       </c>
       <c r="C28" t="n">
-        <v>0.3674</v>
+        <v>0.371</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4266</v>
+        <v>0.4006</v>
       </c>
       <c r="E28" t="n">
-        <v>2.0991</v>
+        <v>2.1197</v>
       </c>
       <c r="F28" t="n">
-        <v>2.3918</v>
+        <v>1.7925</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2927</v>
+        <v>0.3272</v>
       </c>
       <c r="H28" t="n">
-        <v>2.3918</v>
+        <v>1.7925</v>
       </c>
       <c r="I28" t="n">
-        <v>2.4029</v>
+        <v>1.7925</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2927</v>
+        <v>0.3272</v>
       </c>
       <c r="K28" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="L28" t="n">
-        <v>77</v>
+        <v>235</v>
       </c>
       <c r="M28" t="n">
-        <v>2.1102</v>
+        <v>2.1197</v>
       </c>
       <c r="N28" t="n">
-        <v>260</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.0594</v>
+        <v>2.0901</v>
       </c>
       <c r="C29" t="n">
-        <v>0.3605</v>
+        <v>0.3658</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4106</v>
+        <v>0.3888</v>
       </c>
       <c r="E29" t="n">
-        <v>2.0594</v>
+        <v>2.0901</v>
       </c>
       <c r="F29" t="n">
-        <v>2.05</v>
+        <v>2.3828</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0094</v>
+        <v>-0.2927</v>
       </c>
       <c r="H29" t="n">
-        <v>2.05</v>
+        <v>2.3828</v>
       </c>
       <c r="I29" t="n">
-        <v>1.6616</v>
+        <v>2.4029</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0094</v>
+        <v>-0.2927</v>
       </c>
       <c r="K29" t="n">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="L29" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="M29" t="n">
-        <v>1.671</v>
+        <v>2.1102</v>
       </c>
       <c r="N29" t="n">
-        <v>219</v>
+        <v>260</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1.7809</v>
+        <v>2.0594</v>
       </c>
       <c r="C30" t="n">
-        <v>0.3117</v>
+        <v>0.3605</v>
       </c>
       <c r="D30" t="n">
-        <v>0.2981</v>
+        <v>0.3766</v>
       </c>
       <c r="E30" t="n">
-        <v>1.7809</v>
+        <v>2.0594</v>
       </c>
       <c r="F30" t="n">
-        <v>1.7809</v>
+        <v>2.05</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="H30" t="n">
-        <v>1.7809</v>
+        <v>2.05</v>
       </c>
       <c r="I30" t="n">
-        <v>1.7809</v>
+        <v>1.6616</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.0094</v>
       </c>
       <c r="K30" t="n">
-        <v>108</v>
+        <v>155</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M30" t="n">
-        <v>1.7809</v>
+        <v>1.671</v>
       </c>
       <c r="N30" t="n">
-        <v>108</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1.659</v>
+        <v>1.7809</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2904</v>
+        <v>0.3117</v>
       </c>
       <c r="D31" t="n">
-        <v>0.2488</v>
+        <v>0.2656</v>
       </c>
       <c r="E31" t="n">
-        <v>1.659</v>
+        <v>1.7809</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9228</v>
+        <v>1.7809</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7362</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9228</v>
+        <v>1.7809</v>
       </c>
       <c r="I31" t="n">
-        <v>0.9271</v>
+        <v>1.7809</v>
       </c>
       <c r="J31" t="n">
-        <v>0.7362</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="L31" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.6633</v>
+        <v>1.7809</v>
       </c>
       <c r="N31" t="n">
-        <v>260</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Mercury</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1.6424</v>
+        <v>1.6555</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2875</v>
+        <v>0.2898</v>
       </c>
       <c r="D32" t="n">
-        <v>0.2421</v>
+        <v>0.2156</v>
       </c>
       <c r="E32" t="n">
-        <v>1.6424</v>
+        <v>1.6555</v>
       </c>
       <c r="F32" t="n">
-        <v>1.6424</v>
+        <v>0.9193</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.7362</v>
       </c>
       <c r="H32" t="n">
-        <v>1.6424</v>
+        <v>0.9193</v>
       </c>
       <c r="I32" t="n">
-        <v>1.6424</v>
+        <v>0.9271</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.7362</v>
       </c>
       <c r="K32" t="n">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>1.6424</v>
+        <v>1.6633</v>
       </c>
       <c r="N32" t="n">
-        <v>158</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>Mercury</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="C33" t="n">
-        <v>0.252</v>
+        <v>0.2875</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1602</v>
+        <v>0.2104</v>
       </c>
       <c r="E33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>1.4397</v>
+        <v>1.6424</v>
       </c>
       <c r="N33" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1.2792</v>
+        <v>1.3366</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2239</v>
+        <v>0.2339</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0954</v>
+        <v>0.0886</v>
       </c>
       <c r="E34" t="n">
-        <v>1.2792</v>
+        <v>1.3366</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2792</v>
+        <v>1.1385</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>0.1981</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2792</v>
+        <v>1.1385</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2792</v>
+        <v>1.1577</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>0.1981</v>
       </c>
       <c r="K34" t="n">
-        <v>83</v>
+        <v>189</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="M34" t="n">
-        <v>1.2792</v>
+        <v>1.3558</v>
       </c>
       <c r="N34" t="n">
-        <v>83</v>
+        <v>416</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2151</v>
+        <v>0.2239</v>
       </c>
       <c r="D35" t="n">
-        <v>0.075</v>
+        <v>0.06569999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="F35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="I35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.2287</v>
+        <v>1.2792</v>
       </c>
       <c r="N35" t="n">
         <v>83</v>
@@ -2056,32 +2056,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2088</v>
+        <v>0.2151</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0606</v>
+        <v>0.0456</v>
       </c>
       <c r="E36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="F36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="I36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.193</v>
+        <v>1.2287</v>
       </c>
       <c r="N36" t="n">
         <v>83</v>
@@ -2102,93 +2102,93 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9907</v>
+        <v>1.193</v>
       </c>
       <c r="C37" t="n">
-        <v>0.1734</v>
+        <v>0.2088</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0211</v>
+        <v>0.0314</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9907</v>
+        <v>1.193</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9907</v>
+        <v>1.193</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9907</v>
+        <v>1.193</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9953</v>
+        <v>1.193</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.9953</v>
+        <v>1.193</v>
       </c>
       <c r="N37" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.723</v>
+        <v>1.0328</v>
       </c>
       <c r="C38" t="n">
-        <v>0.1265</v>
+        <v>0.1808</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.1293</v>
+        <v>-0.0324</v>
       </c>
       <c r="E38" t="n">
-        <v>0.723</v>
+        <v>1.0328</v>
       </c>
       <c r="F38" t="n">
-        <v>0.723</v>
+        <v>1.4344</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
       <c r="H38" t="n">
-        <v>0.723</v>
+        <v>1.4344</v>
       </c>
       <c r="I38" t="n">
-        <v>0.723</v>
+        <v>1.1626</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4016</v>
       </c>
       <c r="K38" t="n">
-        <v>103</v>
+        <v>155</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M38" t="n">
-        <v>0.723</v>
+        <v>0.7610000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>103</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1075</v>
+        <v>0.1795</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.1732</v>
+        <v>-0.0352</v>
       </c>
       <c r="E39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>0.6142</v>
+        <v>1.0258</v>
       </c>
       <c r="N39" t="n">
         <v>158</v>
@@ -2240,262 +2240,262 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.509</v>
+        <v>0.987</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0891</v>
+        <v>0.1728</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.2157</v>
+        <v>-0.0507</v>
       </c>
       <c r="E40" t="n">
-        <v>0.509</v>
+        <v>0.987</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9106</v>
+        <v>0.987</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9106</v>
+        <v>0.987</v>
       </c>
       <c r="I40" t="n">
-        <v>0.7381</v>
+        <v>0.9953</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.4016</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="L40" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0.3365</v>
+        <v>0.9953</v>
       </c>
       <c r="N40" t="n">
-        <v>219</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.423</v>
+        <v>0.723</v>
       </c>
       <c r="C41" t="n">
-        <v>0.074</v>
+        <v>0.1265</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.2505</v>
+        <v>-0.1559</v>
       </c>
       <c r="E41" t="n">
-        <v>0.423</v>
+        <v>0.723</v>
       </c>
       <c r="F41" t="n">
-        <v>0.2249</v>
+        <v>0.723</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1981</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0.2249</v>
+        <v>0.723</v>
       </c>
       <c r="I41" t="n">
-        <v>0.227</v>
+        <v>0.723</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1981</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>189</v>
+        <v>103</v>
       </c>
       <c r="L41" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>0.4251</v>
+        <v>0.723</v>
       </c>
       <c r="N41" t="n">
-        <v>416</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>biguzera</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.3442</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0602</v>
+        <v>0.095</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.2823</v>
+        <v>-0.2277</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3442</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3442</v>
+        <v>-0.1901</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>0.7329</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3442</v>
+        <v>-0.1901</v>
       </c>
       <c r="I42" t="n">
-        <v>0.3442</v>
+        <v>-0.1901</v>
       </c>
       <c r="J42" t="n">
-        <v>0</v>
+        <v>0.7329</v>
       </c>
       <c r="K42" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="M42" t="n">
-        <v>0.3442</v>
+        <v>0.5427999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>130</v>
+        <v>372</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>jackasmo</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.3283</v>
+        <v>0.3902</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0575</v>
+        <v>0.0683</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2887</v>
+        <v>-0.2885</v>
       </c>
       <c r="E43" t="n">
-        <v>0.3283</v>
+        <v>0.3902</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3283</v>
+        <v>0.4784</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>-0.0882</v>
       </c>
       <c r="H43" t="n">
-        <v>0.3283</v>
+        <v>0.4784</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3298</v>
+        <v>0.4784</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>-0.0882</v>
       </c>
       <c r="K43" t="n">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M43" t="n">
-        <v>0.3298</v>
+        <v>0.3902</v>
       </c>
       <c r="N43" t="n">
-        <v>164</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jackasmo</t>
+          <t>biguzera</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.2931</v>
+        <v>0.3442</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0513</v>
+        <v>0.0602</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.303</v>
+        <v>-0.3068</v>
       </c>
       <c r="E44" t="n">
-        <v>0.2931</v>
+        <v>0.3442</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3813</v>
+        <v>0.3442</v>
       </c>
       <c r="G44" t="n">
-        <v>-0.0882</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3813</v>
+        <v>0.3442</v>
       </c>
       <c r="I44" t="n">
-        <v>0.3813</v>
+        <v>0.3442</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.0882</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.2931</v>
+        <v>0.3442</v>
       </c>
       <c r="N44" t="n">
-        <v>205</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tO0RO</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.2408</v>
+        <v>0.327</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0421</v>
+        <v>0.0572</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3241</v>
+        <v>-0.3136</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2408</v>
+        <v>0.327</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2408</v>
+        <v>0.327</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.2408</v>
+        <v>0.327</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2419</v>
+        <v>0.3298</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.2419</v>
+        <v>0.3298</v>
       </c>
       <c r="N45" t="n">
         <v>164</v>
@@ -2516,231 +2516,231 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>tO0RO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.1652</v>
+        <v>0.2399</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0289</v>
+        <v>0.042</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3546</v>
+        <v>-0.3483</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1652</v>
+        <v>0.2399</v>
       </c>
       <c r="F46" t="n">
-        <v>0.1652</v>
+        <v>0.2399</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.1652</v>
+        <v>0.2399</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1652</v>
+        <v>0.2419</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1652</v>
+        <v>0.2419</v>
       </c>
       <c r="N46" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1652</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0139</v>
+        <v>0.0289</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3894</v>
+        <v>-0.3781</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07920000000000001</v>
+        <v>0.1652</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7523</v>
+        <v>0.1652</v>
       </c>
       <c r="G47" t="n">
-        <v>-0.6731</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.7523</v>
+        <v>0.1652</v>
       </c>
       <c r="I47" t="n">
-        <v>0.7523</v>
+        <v>0.1652</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.6731</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.07919999999999994</v>
+        <v>0.1652</v>
       </c>
       <c r="N47" t="n">
-        <v>205</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.051</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0089</v>
+        <v>0.0139</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.4008</v>
+        <v>-0.4124</v>
       </c>
       <c r="E48" t="n">
-        <v>0.051</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.051</v>
+        <v>0.7523</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>-0.6731</v>
       </c>
       <c r="H48" t="n">
-        <v>0.051</v>
+        <v>0.7523</v>
       </c>
       <c r="I48" t="n">
-        <v>0.051</v>
+        <v>0.7523</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>-0.6731</v>
       </c>
       <c r="K48" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M48" t="n">
-        <v>0.051</v>
+        <v>0.07919999999999994</v>
       </c>
       <c r="N48" t="n">
-        <v>108</v>
+        <v>205</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>-0.0711</v>
+        <v>0.065</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.0124</v>
+        <v>0.0114</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.4501</v>
+        <v>-0.418</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.0711</v>
+        <v>0.065</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.004</v>
+        <v>0.065</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.004</v>
+        <v>0.065</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.0032</v>
+        <v>0.065</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.06710000000000001</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>174</v>
+        <v>95</v>
       </c>
       <c r="L49" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.0703</v>
+        <v>0.065</v>
       </c>
       <c r="N49" t="n">
-        <v>229</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>karrigan</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>-0.2153</v>
+        <v>0.051</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0377</v>
+        <v>0.0089</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.5083</v>
+        <v>-0.4236</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.2153</v>
+        <v>0.051</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.2153</v>
+        <v>0.051</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.2153</v>
+        <v>0.051</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.2163</v>
+        <v>0.051</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>238</v>
+        <v>108</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.2163</v>
+        <v>0.051</v>
       </c>
       <c r="N50" t="n">
-        <v>238</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51">
@@ -2750,28 +2750,28 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>-0.2192</v>
+        <v>-0.0041</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.0384</v>
+        <v>-0.0007</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.5099</v>
+        <v>-0.4455</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.2192</v>
+        <v>-0.0041</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.6857</v>
+        <v>-0.4706</v>
       </c>
       <c r="G51" t="n">
         <v>0.4665</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.6857</v>
+        <v>-0.4706</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.5558</v>
+        <v>-0.3814</v>
       </c>
       <c r="J51" t="n">
         <v>0.4665</v>
@@ -2783,7 +2783,7 @@
         <v>55</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.08929999999999993</v>
+        <v>0.08510000000000001</v>
       </c>
       <c r="N51" t="n">
         <v>229</v>
@@ -2792,216 +2792,216 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>-0.254</v>
+        <v>-0.0711</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.0445</v>
+        <v>-0.0124</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.524</v>
+        <v>-0.4722</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.254</v>
+        <v>-0.0711</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.254</v>
+        <v>-0.004</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.254</v>
+        <v>-0.004</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.254</v>
+        <v>-0.0032</v>
       </c>
       <c r="J52" t="n">
-        <v>0</v>
+        <v>-0.06710000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>108</v>
+        <v>174</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.254</v>
+        <v>-0.0703</v>
       </c>
       <c r="N52" t="n">
-        <v>108</v>
+        <v>229</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kl1m</t>
+          <t>karrigan</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2145</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.0536</v>
+        <v>-0.0375</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.5451</v>
+        <v>-0.5294</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2145</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2145</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2145</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2163</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>95</v>
+        <v>238</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.3063</v>
+        <v>-0.2163</v>
       </c>
       <c r="N53" t="n">
-        <v>95</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.059</v>
+        <v>-0.0445</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.5575</v>
+        <v>-0.5451</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.337</v>
+        <v>-0.254</v>
       </c>
       <c r="N54" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>kl1m</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.3879</v>
+        <v>-0.3063</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.0679</v>
+        <v>-0.0536</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.5659</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.3879</v>
+        <v>-0.3063</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.1208</v>
+        <v>-0.3063</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7329</v>
+        <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.1208</v>
+        <v>-0.3063</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.1208</v>
+        <v>-0.3063</v>
       </c>
       <c r="J55" t="n">
-        <v>0.7329</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>137</v>
+        <v>95</v>
       </c>
       <c r="L55" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.3879</v>
+        <v>-0.3063</v>
       </c>
       <c r="N55" t="n">
-        <v>372</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>zevy</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0701</v>
+        <v>-0.059</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.5831</v>
+        <v>-0.5782</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -3013,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.4004</v>
+        <v>-0.337</v>
       </c>
       <c r="N56" t="n">
         <v>103</v>
@@ -3022,216 +3022,216 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>xerolte</t>
+          <t>zevy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.0701</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6019</v>
+        <v>-0.6034</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.4469</v>
+        <v>-0.4004</v>
       </c>
       <c r="N57" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>xerolte</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.097</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6452</v>
+        <v>-0.622</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.5542</v>
+        <v>-0.4469</v>
       </c>
       <c r="N58" t="n">
-        <v>83</v>
+        <v>56</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>headtr1ck</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.1051</v>
+        <v>-0.097</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6639</v>
+        <v>-0.6647</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.6002999999999999</v>
+        <v>-0.5542</v>
       </c>
       <c r="N59" t="n">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>headtr1ck</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.6683</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.117</v>
+        <v>-0.1051</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6913</v>
+        <v>-0.6831</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.6683</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3317</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="G60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3317</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3332</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="L60" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.6668000000000001</v>
+        <v>-0.6002999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>260</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.1194</v>
+        <v>-0.1058</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6969</v>
+        <v>-0.6847</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3243,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.6820000000000001</v>
+        <v>-0.6045</v>
       </c>
       <c r="N61" t="n">
         <v>158</v>
@@ -3252,231 +3252,231 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Lucaozy</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.7516</v>
+        <v>-0.6696</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.1316</v>
+        <v>-0.1172</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.725</v>
+        <v>-0.7107</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.7516</v>
+        <v>-0.6696</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.7516</v>
+        <v>0.3304</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.7516</v>
+        <v>0.3304</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.7516</v>
+        <v>0.3332</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K62" t="n">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.7516</v>
+        <v>-0.6668000000000001</v>
       </c>
       <c r="N62" t="n">
-        <v>103</v>
+        <v>260</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.1398</v>
+        <v>-0.1194</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7441</v>
+        <v>-0.7156</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.799</v>
+        <v>-0.6820000000000001</v>
       </c>
       <c r="N63" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>Lucaozy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.1474</v>
+        <v>-0.1316</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7617</v>
+        <v>-0.7433</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.8424</v>
+        <v>-0.7516</v>
       </c>
       <c r="N64" t="n">
-        <v>158</v>
+        <v>103</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>z4kr</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.148</v>
+        <v>-0.1398</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.763</v>
+        <v>-0.7622</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.8457</v>
+        <v>-0.799</v>
       </c>
       <c r="N65" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.1515</v>
+        <v>-0.1474</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.7711</v>
+        <v>-0.7795</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.8657</v>
+        <v>-0.8424</v>
       </c>
       <c r="N66" t="n">
-        <v>95</v>
+        <v>158</v>
       </c>
     </row>
     <row r="67">
@@ -3492,7 +3492,7 @@
         <v>-0.1528</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7741</v>
+        <v>-0.7917999999999999</v>
       </c>
       <c r="E67" t="n">
         <v>-0.8732</v>
@@ -3538,7 +3538,7 @@
         <v>-0.1655</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8033</v>
+        <v>-0.8206</v>
       </c>
       <c r="E68" t="n">
         <v>-0.9454</v>
@@ -3584,7 +3584,7 @@
         <v>-0.1676</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.8081</v>
+        <v>-0.8253</v>
       </c>
       <c r="E69" t="n">
         <v>-0.9573</v>
@@ -3630,7 +3630,7 @@
         <v>-0.1734</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.8215</v>
+        <v>-0.8385</v>
       </c>
       <c r="E70" t="n">
         <v>-0.9905</v>
@@ -3676,7 +3676,7 @@
         <v>-0.1919</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.8642</v>
+        <v>-0.8806</v>
       </c>
       <c r="E71" t="n">
         <v>-1.0962</v>
@@ -3722,7 +3722,7 @@
         <v>-0.2029</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.8897</v>
+        <v>-0.9058</v>
       </c>
       <c r="E72" t="n">
         <v>-1.1593</v>
@@ -3768,7 +3768,7 @@
         <v>-0.2036</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.8912</v>
+        <v>-0.9072</v>
       </c>
       <c r="E73" t="n">
         <v>-1.163</v>
@@ -3814,7 +3814,7 @@
         <v>-0.2056</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.8959</v>
+        <v>-0.9119</v>
       </c>
       <c r="E74" t="n">
         <v>-1.1747</v>
@@ -3860,7 +3860,7 @@
         <v>-0.2129</v>
       </c>
       <c r="D75" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.9286</v>
       </c>
       <c r="E75" t="n">
         <v>-1.2165</v>
@@ -3906,7 +3906,7 @@
         <v>-0.2138</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-0.9306</v>
       </c>
       <c r="E76" t="n">
         <v>-1.2215</v>
@@ -3952,7 +3952,7 @@
         <v>-0.2296</v>
       </c>
       <c r="D77" t="n">
-        <v>-0.9513</v>
+        <v>-0.9666</v>
       </c>
       <c r="E77" t="n">
         <v>-1.3119</v>
@@ -3998,7 +3998,7 @@
         <v>-0.3305</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.1842</v>
+        <v>-1.1962</v>
       </c>
       <c r="E78" t="n">
         <v>-1.8882</v>
@@ -4044,7 +4044,7 @@
         <v>-0.3463</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2207</v>
+        <v>-1.2322</v>
       </c>
       <c r="E79" t="n">
         <v>-1.9787</v>
@@ -4084,25 +4084,25 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-2.256</v>
+        <v>-2.2476</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.3949</v>
+        <v>-0.3934</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3327</v>
+        <v>-1.3394</v>
       </c>
       <c r="E80" t="n">
-        <v>-2.256</v>
+        <v>-2.2476</v>
       </c>
       <c r="F80" t="n">
-        <v>-2.256</v>
+        <v>-2.2476</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-2.256</v>
+        <v>-2.2476</v>
       </c>
       <c r="I80" t="n">
         <v>-2.2665</v>
@@ -4136,7 +4136,7 @@
         <v>-0.5384</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6639</v>
+        <v>-1.6693</v>
       </c>
       <c r="E81" t="n">
         <v>-3.0758</v>

--- a/database/event/8027/event_8027_evp_summary.xlsx
+++ b/database/event/8027/event_8027_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5167</v>
+        <v>8.6951</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4907</v>
+        <v>1.5219</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2528</v>
+        <v>3.2701</v>
       </c>
       <c r="E2" t="n">
-        <v>8.5167</v>
+        <v>8.6951</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1759</v>
+        <v>3.1763</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3408</v>
+        <v>5.341</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2262</v>
+        <v>4.227</v>
       </c>
       <c r="I2" t="n">
-        <v>4.2262</v>
+        <v>4.227</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3408</v>
+        <v>5.341</v>
       </c>
       <c r="K2" t="n">
         <v>137</v>
@@ -529,7 +529,7 @@
         <v>235</v>
       </c>
       <c r="M2" t="n">
-        <v>9.567</v>
+        <v>9.568000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>372</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.3186</v>
+        <v>5.2082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9308999999999999</v>
+        <v>0.9116</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7969</v>
+        <v>1.7126</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3186</v>
+        <v>5.2082</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6209</v>
+        <v>2.621</v>
       </c>
       <c r="G3" t="n">
-        <v>2.6977</v>
+        <v>2.6812</v>
       </c>
       <c r="H3" t="n">
-        <v>3.0113</v>
+        <v>3.0116</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0113</v>
+        <v>3.0116</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6977</v>
+        <v>2.6812</v>
       </c>
       <c r="K3" t="n">
         <v>137</v>
@@ -575,7 +575,7 @@
         <v>235</v>
       </c>
       <c r="M3" t="n">
-        <v>5.709</v>
+        <v>5.6928</v>
       </c>
       <c r="N3" t="n">
         <v>372</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.296</v>
+        <v>4.3683</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7519</v>
+        <v>0.7645999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3314</v>
+        <v>1.3374</v>
       </c>
       <c r="E4" t="n">
-        <v>4.296</v>
+        <v>4.3683</v>
       </c>
       <c r="F4" t="n">
-        <v>2.5808</v>
+        <v>2.5806</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7152</v>
+        <v>1.7294</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9236</v>
+        <v>2.9233</v>
       </c>
       <c r="I4" t="n">
-        <v>3.0762</v>
+        <v>3.0759</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7152</v>
+        <v>1.7294</v>
       </c>
       <c r="K4" t="n">
         <v>189</v>
@@ -621,7 +621,7 @@
         <v>227</v>
       </c>
       <c r="M4" t="n">
-        <v>4.7914</v>
+        <v>4.8053</v>
       </c>
       <c r="N4" t="n">
         <v>416</v>
@@ -630,323 +630,323 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0006</v>
+        <v>4.005</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7002</v>
+        <v>0.701</v>
       </c>
       <c r="D5" t="n">
-        <v>1.197</v>
+        <v>1.1751</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0006</v>
+        <v>4.005</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1391</v>
+        <v>3.6701</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8615</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1634</v>
+        <v>5.3078</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1682</v>
+        <v>5.4446</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8615</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>174</v>
+        <v>238</v>
       </c>
       <c r="L5" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.0297</v>
+        <v>5.4446</v>
       </c>
       <c r="N5" t="n">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7661</v>
+        <v>3.9923</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6592</v>
+        <v>0.6988</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0902</v>
+        <v>1.1695</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7661</v>
+        <v>3.9923</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4326</v>
+        <v>2.1292</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3335</v>
+        <v>1.8615</v>
       </c>
       <c r="H6" t="n">
-        <v>6.4314</v>
+        <v>2.131</v>
       </c>
       <c r="I6" t="n">
-        <v>3.4729</v>
+        <v>1.1507</v>
       </c>
       <c r="J6" t="n">
-        <v>0.3335</v>
+        <v>1.8615</v>
       </c>
       <c r="K6" t="n">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="L6" t="n">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="M6" t="n">
-        <v>3.8064</v>
+        <v>3.0122</v>
       </c>
       <c r="N6" t="n">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>blameF</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.7587</v>
+        <v>3.9297</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6579</v>
+        <v>0.6878</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0868</v>
+        <v>1.1415</v>
       </c>
       <c r="E7" t="n">
-        <v>3.7587</v>
+        <v>3.9297</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4284</v>
+        <v>2.908</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3303</v>
+        <v>0.731</v>
       </c>
       <c r="H7" t="n">
-        <v>2.59</v>
+        <v>3.6398</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7252</v>
+        <v>3.6398</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3303</v>
+        <v>0.731</v>
       </c>
       <c r="K7" t="n">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="L7" t="n">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="M7" t="n">
-        <v>4.0555</v>
+        <v>4.3708</v>
       </c>
       <c r="N7" t="n">
-        <v>416</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.6678</v>
+        <v>3.858</v>
       </c>
       <c r="C8" t="n">
-        <v>0.642</v>
+        <v>0.6753</v>
       </c>
       <c r="D8" t="n">
-        <v>1.0455</v>
+        <v>1.1095</v>
       </c>
       <c r="E8" t="n">
-        <v>3.6678</v>
+        <v>3.858</v>
       </c>
       <c r="F8" t="n">
-        <v>3.6678</v>
+        <v>2.4282</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.3385</v>
       </c>
       <c r="H8" t="n">
-        <v>5.3028</v>
+        <v>2.5897</v>
       </c>
       <c r="I8" t="n">
-        <v>5.4394</v>
+        <v>2.7249</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.3385</v>
       </c>
       <c r="K8" t="n">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="M8" t="n">
-        <v>5.4394</v>
+        <v>4.0634</v>
       </c>
       <c r="N8" t="n">
-        <v>238</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>blameF</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.64</v>
+        <v>3.7163</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6371</v>
+        <v>0.6505</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0328</v>
+        <v>1.0462</v>
       </c>
       <c r="E9" t="n">
-        <v>3.64</v>
+        <v>3.7163</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9087</v>
+        <v>3.4328</v>
       </c>
       <c r="G9" t="n">
-        <v>0.7313</v>
+        <v>0.3335</v>
       </c>
       <c r="H9" t="n">
-        <v>3.6414</v>
+        <v>6.432</v>
       </c>
       <c r="I9" t="n">
-        <v>3.6414</v>
+        <v>3.4732</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7313</v>
+        <v>0.3335</v>
       </c>
       <c r="K9" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L9" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M9" t="n">
-        <v>4.3727</v>
+        <v>3.8067</v>
       </c>
       <c r="N9" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>dziugss</t>
+          <t>hades</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.4887</v>
+        <v>3.6747</v>
       </c>
       <c r="C10" t="n">
-        <v>0.6106</v>
+        <v>0.6432</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9639</v>
+        <v>1.0276</v>
       </c>
       <c r="E10" t="n">
-        <v>3.4887</v>
+        <v>3.6747</v>
       </c>
       <c r="F10" t="n">
-        <v>2.4156</v>
+        <v>4.004</v>
       </c>
       <c r="G10" t="n">
-        <v>1.0731</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.562</v>
+        <v>8.3164</v>
       </c>
       <c r="I10" t="n">
-        <v>2.628</v>
+        <v>4.4908</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0731</v>
+        <v>-0.5731000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="L10" t="n">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.7011</v>
+        <v>3.9177</v>
       </c>
       <c r="N10" t="n">
-        <v>260</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hades</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.4287</v>
+        <v>3.528</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6001</v>
+        <v>0.6175</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9366</v>
+        <v>0.9621</v>
       </c>
       <c r="E11" t="n">
-        <v>3.4287</v>
+        <v>3.528</v>
       </c>
       <c r="F11" t="n">
-        <v>4.0018</v>
+        <v>3.85</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.4767</v>
       </c>
       <c r="H11" t="n">
-        <v>8.3094</v>
+        <v>7.8083</v>
       </c>
       <c r="I11" t="n">
-        <v>4.487</v>
+        <v>4.2164</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5731000000000001</v>
+        <v>-0.4767</v>
       </c>
       <c r="K11" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="L11" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="M11" t="n">
-        <v>3.9139</v>
+        <v>3.7397</v>
       </c>
       <c r="N11" t="n">
-        <v>229</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.4118</v>
+        <v>3.4517</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5972</v>
+        <v>0.6042</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.928</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4118</v>
+        <v>3.4517</v>
       </c>
       <c r="F12" t="n">
-        <v>3.4018</v>
+        <v>3.4019</v>
       </c>
       <c r="G12" t="n">
         <v>0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>6.3297</v>
+        <v>6.3301</v>
       </c>
       <c r="I12" t="n">
-        <v>3.418</v>
+        <v>3.4182</v>
       </c>
       <c r="J12" t="n">
         <v>0.01</v>
@@ -989,7 +989,7 @@
         <v>64</v>
       </c>
       <c r="M12" t="n">
-        <v>3.428</v>
+        <v>3.4282</v>
       </c>
       <c r="N12" t="n">
         <v>219</v>
@@ -998,185 +998,185 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lucky</t>
+          <t>dziugss</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.3773</v>
+        <v>3.4129</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5911</v>
+        <v>0.5974</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9132</v>
+        <v>0.9106</v>
       </c>
       <c r="E13" t="n">
-        <v>3.3773</v>
+        <v>3.4129</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4364</v>
+        <v>2.4243</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9409</v>
+        <v>1.0726</v>
       </c>
       <c r="H13" t="n">
-        <v>2.6075</v>
+        <v>2.5811</v>
       </c>
       <c r="I13" t="n">
-        <v>2.7436</v>
+        <v>2.6476</v>
       </c>
       <c r="J13" t="n">
-        <v>0.9409</v>
+        <v>1.0726</v>
       </c>
       <c r="K13" t="n">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="L13" t="n">
-        <v>227</v>
+        <v>77</v>
       </c>
       <c r="M13" t="n">
-        <v>3.6845</v>
+        <v>3.7202</v>
       </c>
       <c r="N13" t="n">
-        <v>416</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.3731</v>
+        <v>3.4061</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5904</v>
+        <v>0.5962</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9113</v>
+        <v>0.9076</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3731</v>
+        <v>3.4061</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8498</v>
+        <v>3.1988</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.4767</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>7.8079</v>
+        <v>4.2763</v>
       </c>
       <c r="I14" t="n">
-        <v>4.2162</v>
+        <v>4.3865</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.4767</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="L14" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.7395</v>
+        <v>4.3865</v>
       </c>
       <c r="N14" t="n">
-        <v>219</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>Lucky</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.331</v>
+        <v>3.4055</v>
       </c>
       <c r="C15" t="n">
-        <v>0.583</v>
+        <v>0.5961</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8921</v>
+        <v>0.9073</v>
       </c>
       <c r="E15" t="n">
-        <v>3.331</v>
+        <v>3.4055</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1035</v>
+        <v>2.4453</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2275</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1035</v>
+        <v>2.6272</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1035</v>
+        <v>2.7643</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2275</v>
+        <v>0.9550999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>137</v>
+        <v>189</v>
       </c>
       <c r="L15" t="n">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="M15" t="n">
-        <v>3.331</v>
+        <v>3.7194</v>
       </c>
       <c r="N15" t="n">
-        <v>372</v>
+        <v>416</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>jambo</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3273</v>
+        <v>3.3903</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5824</v>
+        <v>0.5934</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8905</v>
+        <v>0.9006</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3273</v>
+        <v>3.3903</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1866</v>
+        <v>2.6452</v>
       </c>
       <c r="G16" t="n">
-        <v>2.1407</v>
+        <v>0.3725</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1866</v>
+        <v>3.0646</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2485</v>
+        <v>3.0646</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1407</v>
+        <v>0.3725</v>
       </c>
       <c r="K16" t="n">
-        <v>189</v>
+        <v>145</v>
       </c>
       <c r="L16" t="n">
-        <v>227</v>
+        <v>60</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3892</v>
+        <v>3.4371</v>
       </c>
       <c r="N16" t="n">
-        <v>416</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.2639</v>
+        <v>3.3209</v>
       </c>
       <c r="C17" t="n">
-        <v>0.5713</v>
+        <v>0.5813</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8616</v>
+        <v>0.8696</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2639</v>
+        <v>3.3209</v>
       </c>
       <c r="F17" t="n">
-        <v>3.2639</v>
+        <v>3.2593</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4187</v>
+        <v>4.4087</v>
       </c>
       <c r="I17" t="n">
-        <v>4.5326</v>
+        <v>4.5223</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>4.5326</v>
+        <v>4.5223</v>
       </c>
       <c r="N17" t="n">
         <v>238</v>
@@ -1228,93 +1228,93 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.2097</v>
+        <v>3.2933</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5618</v>
+        <v>0.5764</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8369</v>
+        <v>0.8572</v>
       </c>
       <c r="E18" t="n">
-        <v>3.2097</v>
+        <v>3.2933</v>
       </c>
       <c r="F18" t="n">
-        <v>3.2097</v>
+        <v>2.0775</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>2.0775</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4108</v>
+        <v>2.0775</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="K18" t="n">
-        <v>238</v>
+        <v>137</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="M18" t="n">
-        <v>4.4108</v>
+        <v>3.3052</v>
       </c>
       <c r="N18" t="n">
-        <v>238</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>jambo</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.0187</v>
+        <v>3.2629</v>
       </c>
       <c r="C19" t="n">
-        <v>0.5284</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>0.75</v>
+        <v>0.8436</v>
       </c>
       <c r="E19" t="n">
-        <v>3.0187</v>
+        <v>3.2629</v>
       </c>
       <c r="F19" t="n">
-        <v>2.646</v>
+        <v>1.1863</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3727</v>
+        <v>2.139</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0663</v>
+        <v>1.1863</v>
       </c>
       <c r="I19" t="n">
-        <v>3.0663</v>
+        <v>1.2482</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3727</v>
+        <v>2.139</v>
       </c>
       <c r="K19" t="n">
-        <v>145</v>
+        <v>189</v>
       </c>
       <c r="L19" t="n">
-        <v>60</v>
+        <v>227</v>
       </c>
       <c r="M19" t="n">
-        <v>3.439</v>
+        <v>3.3872</v>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>416</v>
       </c>
     </row>
     <row r="20">
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.9454</v>
+        <v>3.148</v>
       </c>
       <c r="C20" t="n">
-        <v>0.5155</v>
+        <v>0.551</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7166</v>
+        <v>0.7923</v>
       </c>
       <c r="E20" t="n">
-        <v>2.9454</v>
+        <v>3.148</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9631</v>
+        <v>2.9715</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0177</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8822</v>
+        <v>4.91</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6363</v>
+        <v>2.6513</v>
       </c>
       <c r="J20" t="n">
         <v>-0.0177</v>
@@ -1357,7 +1357,7 @@
         <v>55</v>
       </c>
       <c r="M20" t="n">
-        <v>2.6186</v>
+        <v>2.6336</v>
       </c>
       <c r="N20" t="n">
         <v>229</v>
@@ -1366,47 +1366,47 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2.9053</v>
+        <v>3.0753</v>
       </c>
       <c r="C21" t="n">
-        <v>0.5085</v>
+        <v>0.5383</v>
       </c>
       <c r="D21" t="n">
-        <v>0.6983</v>
+        <v>0.7598</v>
       </c>
       <c r="E21" t="n">
-        <v>2.9053</v>
+        <v>3.0753</v>
       </c>
       <c r="F21" t="n">
-        <v>2.7925</v>
+        <v>2.7607</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1128</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3869</v>
+        <v>3.3173</v>
       </c>
       <c r="I21" t="n">
-        <v>3.4742</v>
+        <v>3.3173</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1128</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>183</v>
+        <v>130</v>
       </c>
       <c r="L21" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.587</v>
+        <v>3.3173</v>
       </c>
       <c r="N21" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22">
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2.8609</v>
+        <v>3.0553</v>
       </c>
       <c r="C22" t="n">
-        <v>0.5007</v>
+        <v>0.5348000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6781</v>
+        <v>0.7509</v>
       </c>
       <c r="E22" t="n">
-        <v>2.8609</v>
+        <v>3.0553</v>
       </c>
       <c r="F22" t="n">
-        <v>2.8609</v>
+        <v>2.8603</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.5367</v>
+        <v>3.5353</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6278</v>
+        <v>3.6264</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.6278</v>
+        <v>3.6264</v>
       </c>
       <c r="N22" t="n">
         <v>164</v>
@@ -1458,139 +1458,139 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dumau</t>
+          <t>dav1deuS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2.8238</v>
+        <v>3.0492</v>
       </c>
       <c r="C23" t="n">
-        <v>0.4942</v>
+        <v>0.5337</v>
       </c>
       <c r="D23" t="n">
-        <v>0.6612</v>
+        <v>0.7482</v>
       </c>
       <c r="E23" t="n">
-        <v>2.8238</v>
+        <v>3.0492</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2156</v>
+        <v>2.8053</v>
       </c>
       <c r="G23" t="n">
-        <v>2.6082</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.2156</v>
+        <v>3.4149</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2156</v>
+        <v>3.4149</v>
       </c>
       <c r="J23" t="n">
-        <v>2.6082</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="L23" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.8238</v>
+        <v>3.4149</v>
       </c>
       <c r="N23" t="n">
-        <v>372</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>dav1deuS</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.8126</v>
+        <v>3.0458</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4923</v>
+        <v>0.5331</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6562</v>
+        <v>0.7467</v>
       </c>
       <c r="E24" t="n">
-        <v>2.8126</v>
+        <v>3.0458</v>
       </c>
       <c r="F24" t="n">
-        <v>2.8126</v>
+        <v>2.7964</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="H24" t="n">
-        <v>3.4309</v>
+        <v>3.3954</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4309</v>
+        <v>3.4829</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.1565</v>
       </c>
       <c r="K24" t="n">
-        <v>130</v>
+        <v>183</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4309</v>
+        <v>3.6394</v>
       </c>
       <c r="N24" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>npl</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.7534</v>
+        <v>2.9753</v>
       </c>
       <c r="C25" t="n">
-        <v>0.4819</v>
+        <v>0.5208</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6292</v>
+        <v>0.7151999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>2.7534</v>
+        <v>2.9753</v>
       </c>
       <c r="F25" t="n">
-        <v>2.7534</v>
+        <v>2.3744</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.3015</v>
+        <v>2.4718</v>
       </c>
       <c r="I25" t="n">
-        <v>3.3015</v>
+        <v>2.4718</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.3015</v>
+        <v>2.4718</v>
       </c>
       <c r="N25" t="n">
-        <v>130</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.7514</v>
+        <v>2.9227</v>
       </c>
       <c r="C26" t="n">
-        <v>0.4816</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6283</v>
+        <v>0.6917</v>
       </c>
       <c r="E26" t="n">
-        <v>2.7514</v>
+        <v>2.9227</v>
       </c>
       <c r="F26" t="n">
-        <v>2.7514</v>
+        <v>2.7518</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2971</v>
+        <v>3.2979</v>
       </c>
       <c r="I26" t="n">
-        <v>3.2971</v>
+        <v>3.2979</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2971</v>
+        <v>3.2979</v>
       </c>
       <c r="N26" t="n">
         <v>128</v>
@@ -1642,277 +1642,277 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>dumau</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.6809</v>
+        <v>2.9111</v>
       </c>
       <c r="C27" t="n">
-        <v>0.4692</v>
+        <v>0.5095</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5962</v>
+        <v>0.6865</v>
       </c>
       <c r="E27" t="n">
-        <v>2.6809</v>
+        <v>2.9111</v>
       </c>
       <c r="F27" t="n">
-        <v>2.6397</v>
+        <v>0.1932</v>
       </c>
       <c r="G27" t="n">
-        <v>0.0412</v>
+        <v>2.6086</v>
       </c>
       <c r="H27" t="n">
-        <v>3.8152</v>
+        <v>0.1932</v>
       </c>
       <c r="I27" t="n">
-        <v>2.0602</v>
+        <v>0.1932</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0412</v>
+        <v>2.6086</v>
       </c>
       <c r="K27" t="n">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="L27" t="n">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="M27" t="n">
-        <v>2.1014</v>
+        <v>2.8018</v>
       </c>
       <c r="N27" t="n">
-        <v>219</v>
+        <v>372</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.5706</v>
+        <v>2.7138</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4499</v>
+        <v>0.475</v>
       </c>
       <c r="D28" t="n">
-        <v>0.546</v>
+        <v>0.5984</v>
       </c>
       <c r="E28" t="n">
-        <v>2.5706</v>
+        <v>2.7138</v>
       </c>
       <c r="F28" t="n">
-        <v>1.7828</v>
+        <v>2.6332</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="H28" t="n">
-        <v>1.7828</v>
+        <v>3.7939</v>
       </c>
       <c r="I28" t="n">
-        <v>1.8759</v>
+        <v>2.0486</v>
       </c>
       <c r="J28" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.0412</v>
       </c>
       <c r="K28" t="n">
-        <v>189</v>
+        <v>155</v>
       </c>
       <c r="L28" t="n">
-        <v>227</v>
+        <v>64</v>
       </c>
       <c r="M28" t="n">
-        <v>2.6637</v>
+        <v>2.0898</v>
       </c>
       <c r="N28" t="n">
-        <v>416</v>
+        <v>219</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cmtry</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.5087</v>
+        <v>2.672</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4391</v>
+        <v>0.4677</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5178</v>
+        <v>0.5797</v>
       </c>
       <c r="E29" t="n">
-        <v>2.5087</v>
+        <v>2.672</v>
       </c>
       <c r="F29" t="n">
-        <v>2.5507</v>
+        <v>2.4959</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.042</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.8577</v>
+        <v>2.7378</v>
       </c>
       <c r="I29" t="n">
-        <v>2.9313</v>
+        <v>2.8083</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.042</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="L29" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.8893</v>
+        <v>2.8083</v>
       </c>
       <c r="N29" t="n">
-        <v>260</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.4964</v>
+        <v>2.5345</v>
       </c>
       <c r="C30" t="n">
-        <v>0.4369</v>
+        <v>0.4436</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5122</v>
+        <v>0.5183</v>
       </c>
       <c r="E30" t="n">
-        <v>2.4964</v>
+        <v>2.5345</v>
       </c>
       <c r="F30" t="n">
-        <v>2.4964</v>
+        <v>1.7826</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>0.8021</v>
       </c>
       <c r="H30" t="n">
-        <v>2.7389</v>
+        <v>1.7826</v>
       </c>
       <c r="I30" t="n">
-        <v>2.8095</v>
+        <v>1.8756</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>0.8021</v>
       </c>
       <c r="K30" t="n">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="M30" t="n">
-        <v>2.8095</v>
+        <v>2.6777</v>
       </c>
       <c r="N30" t="n">
-        <v>164</v>
+        <v>416</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>npl</t>
+          <t>insani</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.3745</v>
+        <v>2.5022</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4156</v>
+        <v>0.438</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4567</v>
+        <v>0.5039</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3745</v>
+        <v>2.5022</v>
       </c>
       <c r="F31" t="n">
-        <v>2.3745</v>
+        <v>2.0763</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.472</v>
+        <v>2.0763</v>
       </c>
       <c r="I31" t="n">
-        <v>2.472</v>
+        <v>2.0763</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.472</v>
+        <v>2.0763</v>
       </c>
       <c r="N31" t="n">
-        <v>108</v>
+        <v>95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>cmtry</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.1232</v>
+        <v>2.4908</v>
       </c>
       <c r="C32" t="n">
-        <v>0.3716</v>
+        <v>0.436</v>
       </c>
       <c r="D32" t="n">
-        <v>0.3423</v>
+        <v>0.4988</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1232</v>
+        <v>2.4908</v>
       </c>
       <c r="F32" t="n">
-        <v>2.4151</v>
+        <v>2.5637</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.2919</v>
+        <v>-0.0425</v>
       </c>
       <c r="H32" t="n">
-        <v>3.0742</v>
+        <v>2.8862</v>
       </c>
       <c r="I32" t="n">
-        <v>1.66</v>
+        <v>2.9606</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.2919</v>
+        <v>-0.0425</v>
       </c>
       <c r="K32" t="n">
-        <v>155</v>
+        <v>183</v>
       </c>
       <c r="L32" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="M32" t="n">
-        <v>1.3681</v>
+        <v>2.9181</v>
       </c>
       <c r="N32" t="n">
-        <v>219</v>
+        <v>260</v>
       </c>
     </row>
     <row r="33">
@@ -1922,31 +1922,31 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.1028</v>
+        <v>2.1042</v>
       </c>
       <c r="C33" t="n">
-        <v>0.3681</v>
+        <v>0.3683</v>
       </c>
       <c r="D33" t="n">
-        <v>0.333</v>
+        <v>0.3261</v>
       </c>
       <c r="E33" t="n">
-        <v>2.1028</v>
+        <v>2.1042</v>
       </c>
       <c r="F33" t="n">
-        <v>1.3162</v>
+        <v>1.3154</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7866</v>
+        <v>0.7864</v>
       </c>
       <c r="H33" t="n">
-        <v>1.3162</v>
+        <v>1.3154</v>
       </c>
       <c r="I33" t="n">
-        <v>1.3501</v>
+        <v>1.3493</v>
       </c>
       <c r="J33" t="n">
-        <v>0.7866</v>
+        <v>0.7864</v>
       </c>
       <c r="K33" t="n">
         <v>183</v>
@@ -1955,7 +1955,7 @@
         <v>77</v>
       </c>
       <c r="M33" t="n">
-        <v>2.1367</v>
+        <v>2.1357</v>
       </c>
       <c r="N33" t="n">
         <v>260</v>
@@ -1964,47 +1964,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>insani</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.0763</v>
+        <v>2.0459</v>
       </c>
       <c r="C34" t="n">
-        <v>0.3634</v>
+        <v>0.3581</v>
       </c>
       <c r="D34" t="n">
-        <v>0.321</v>
+        <v>0.3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.0763</v>
+        <v>2.0459</v>
       </c>
       <c r="F34" t="n">
-        <v>2.0763</v>
+        <v>2.4154</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>-0.2919</v>
       </c>
       <c r="H34" t="n">
-        <v>2.0763</v>
+        <v>3.075</v>
       </c>
       <c r="I34" t="n">
-        <v>2.0763</v>
+        <v>1.6604</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>-0.2919</v>
       </c>
       <c r="K34" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="M34" t="n">
-        <v>2.0763</v>
+        <v>1.3685</v>
       </c>
       <c r="N34" t="n">
-        <v>95</v>
+        <v>219</v>
       </c>
     </row>
     <row r="35">
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.929</v>
+        <v>1.8893</v>
       </c>
       <c r="C35" t="n">
-        <v>0.3376</v>
+        <v>0.3307</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2539</v>
+        <v>0.2301</v>
       </c>
       <c r="E35" t="n">
-        <v>1.929</v>
+        <v>1.8893</v>
       </c>
       <c r="F35" t="n">
-        <v>1.929</v>
+        <v>1.9291</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>1.929</v>
+        <v>1.9291</v>
       </c>
       <c r="I35" t="n">
-        <v>1.929</v>
+        <v>1.9291</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.929</v>
+        <v>1.9291</v>
       </c>
       <c r="N35" t="n">
         <v>158</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1.4295</v>
+        <v>1.5946</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2502</v>
+        <v>0.2791</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0265</v>
+        <v>0.0985</v>
       </c>
       <c r="E36" t="n">
-        <v>1.4295</v>
+        <v>1.5946</v>
       </c>
       <c r="F36" t="n">
-        <v>1.4295</v>
+        <v>1.4451</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>1.4295</v>
+        <v>1.4451</v>
       </c>
       <c r="I36" t="n">
-        <v>1.4295</v>
+        <v>1.4451</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.4295</v>
+        <v>1.4451</v>
       </c>
       <c r="N36" t="n">
         <v>83</v>
@@ -2102,185 +2102,185 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Tauson</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1.3478</v>
+        <v>1.4934</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2359</v>
+        <v>0.2614</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.0107</v>
+        <v>0.0532</v>
       </c>
       <c r="E37" t="n">
-        <v>1.3478</v>
+        <v>1.4934</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5782</v>
+        <v>1.3267</v>
       </c>
       <c r="G37" t="n">
-        <v>0.7696</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5782</v>
+        <v>1.3267</v>
       </c>
       <c r="I37" t="n">
-        <v>0.5782</v>
+        <v>1.3267</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7696</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>137</v>
+        <v>83</v>
       </c>
       <c r="L37" t="n">
-        <v>235</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.3478</v>
+        <v>1.3267</v>
       </c>
       <c r="N37" t="n">
-        <v>372</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Tauson</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>1.3279</v>
+        <v>1.3516</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2324</v>
+        <v>0.2366</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.0197</v>
+        <v>-0.0101</v>
       </c>
       <c r="E38" t="n">
-        <v>1.3279</v>
+        <v>1.3516</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3279</v>
+        <v>0.5782</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>0.7698</v>
       </c>
       <c r="H38" t="n">
-        <v>1.3279</v>
+        <v>0.5782</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3279</v>
+        <v>0.5782</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>0.7698</v>
       </c>
       <c r="K38" t="n">
-        <v>83</v>
+        <v>137</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="M38" t="n">
-        <v>1.3279</v>
+        <v>1.348</v>
       </c>
       <c r="N38" t="n">
-        <v>83</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1.3058</v>
+        <v>1.3486</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2286</v>
+        <v>0.236</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.0298</v>
+        <v>-0.0114</v>
       </c>
       <c r="E39" t="n">
-        <v>1.3058</v>
+        <v>1.3486</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3058</v>
+        <v>1.3095</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>1.3058</v>
+        <v>1.3095</v>
       </c>
       <c r="I39" t="n">
-        <v>1.3395</v>
+        <v>1.3095</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>1.3395</v>
+        <v>1.3095</v>
       </c>
       <c r="N39" t="n">
-        <v>164</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.2955</v>
+        <v>1.2096</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2268</v>
+        <v>0.2117</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.0345</v>
+        <v>-0.0735</v>
       </c>
       <c r="E40" t="n">
-        <v>1.2955</v>
+        <v>1.2096</v>
       </c>
       <c r="F40" t="n">
-        <v>1.2955</v>
+        <v>1.305</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.2955</v>
+        <v>1.305</v>
       </c>
       <c r="I40" t="n">
-        <v>1.2955</v>
+        <v>1.3386</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.2955</v>
+        <v>1.3386</v>
       </c>
       <c r="N40" t="n">
-        <v>83</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41">
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.1732</v>
+        <v>1.1932</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2053</v>
+        <v>0.2088</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.0901</v>
+        <v>-0.0808</v>
       </c>
       <c r="E41" t="n">
-        <v>1.1732</v>
+        <v>1.1932</v>
       </c>
       <c r="F41" t="n">
-        <v>1.1732</v>
+        <v>1.1845</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>1.1732</v>
+        <v>1.1845</v>
       </c>
       <c r="I41" t="n">
-        <v>1.1732</v>
+        <v>1.1845</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2323,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1.1732</v>
+        <v>1.1845</v>
       </c>
       <c r="N41" t="n">
         <v>158</v>
@@ -2332,81 +2332,81 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>yxngstxr</t>
+          <t>jackasmo</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9711</v>
+        <v>0.9157</v>
       </c>
       <c r="C42" t="n">
-        <v>0.17</v>
+        <v>0.1603</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.1821</v>
+        <v>-0.2048</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9711</v>
+        <v>0.9157</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3809</v>
+        <v>0.8082</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.0608</v>
       </c>
       <c r="H42" t="n">
-        <v>0.3809</v>
+        <v>0.8082</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2057</v>
+        <v>0.8082</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5901999999999999</v>
+        <v>0.0608</v>
       </c>
       <c r="K42" t="n">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="L42" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7958999999999999</v>
+        <v>0.869</v>
       </c>
       <c r="N42" t="n">
-        <v>229</v>
+        <v>205</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>yxngstxr</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.904</v>
+        <v>0.8083</v>
       </c>
       <c r="C43" t="n">
-        <v>0.1582</v>
+        <v>0.1415</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.2127</v>
+        <v>-0.2528</v>
       </c>
       <c r="E43" t="n">
-        <v>0.904</v>
+        <v>0.8083</v>
       </c>
       <c r="F43" t="n">
-        <v>0.8425</v>
+        <v>0.3628</v>
       </c>
       <c r="G43" t="n">
-        <v>0.0615</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8425</v>
+        <v>0.3628</v>
       </c>
       <c r="I43" t="n">
-        <v>0.455</v>
+        <v>0.1959</v>
       </c>
       <c r="J43" t="n">
-        <v>0.0615</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="K43" t="n">
         <v>174</v>
@@ -2415,7 +2415,7 @@
         <v>55</v>
       </c>
       <c r="M43" t="n">
-        <v>0.5165</v>
+        <v>0.7860999999999999</v>
       </c>
       <c r="N43" t="n">
         <v>229</v>
@@ -2424,47 +2424,47 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>jackasmo</t>
+          <t>kye</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8618</v>
+        <v>0.7177</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1508</v>
+        <v>0.1256</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.2319</v>
+        <v>-0.2932</v>
       </c>
       <c r="E44" t="n">
-        <v>0.8618</v>
+        <v>0.7177</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="G44" t="n">
-        <v>0.0609</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="I44" t="n">
-        <v>0.8008999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0609</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8617999999999999</v>
+        <v>0.6452</v>
       </c>
       <c r="N44" t="n">
-        <v>205</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45">
@@ -2474,28 +2474,28 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="C45" t="n">
-        <v>0.1171</v>
+        <v>0.1239</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.3197</v>
+        <v>-0.2976</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="F45" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6897</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.6689000000000001</v>
+        <v>0.6897</v>
       </c>
       <c r="I45" t="n">
-        <v>0.6861</v>
+        <v>0.7075</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -2507,7 +2507,7 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0.6861</v>
+        <v>0.7075</v>
       </c>
       <c r="N45" t="n">
         <v>164</v>
@@ -2516,185 +2516,185 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>kye</t>
+          <t>kRaSnaL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6589</v>
+        <v>0.6193</v>
       </c>
       <c r="C46" t="n">
-        <v>0.1153</v>
+        <v>0.1084</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.3243</v>
+        <v>-0.3372</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6589</v>
+        <v>0.6193</v>
       </c>
       <c r="F46" t="n">
-        <v>0.6589</v>
+        <v>0.4319</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0.6589</v>
+        <v>0.4319</v>
       </c>
       <c r="I46" t="n">
-        <v>0.6589</v>
+        <v>0.4319</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>0.6589</v>
+        <v>0.4319</v>
       </c>
       <c r="N46" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tO0RO</t>
+          <t>brnz4n</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.658</v>
+        <v>0.5754</v>
       </c>
       <c r="C47" t="n">
-        <v>0.1152</v>
+        <v>0.1007</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.3247</v>
+        <v>-0.3568</v>
       </c>
       <c r="E47" t="n">
-        <v>0.658</v>
+        <v>0.5754</v>
       </c>
       <c r="F47" t="n">
-        <v>0.658</v>
+        <v>0.6233</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.658</v>
+        <v>0.6233</v>
       </c>
       <c r="I47" t="n">
-        <v>0.675</v>
+        <v>0.6233</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0.675</v>
+        <v>0.6233</v>
       </c>
       <c r="N47" t="n">
-        <v>164</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>brnz4n</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6233</v>
+        <v>0.5472</v>
       </c>
       <c r="C48" t="n">
-        <v>0.1091</v>
+        <v>0.0958</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.3405</v>
+        <v>-0.3694</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6233</v>
+        <v>0.5472</v>
       </c>
       <c r="F48" t="n">
-        <v>0.6233</v>
+        <v>0.6375</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6233</v>
+        <v>0.6375</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6233</v>
+        <v>0.3443</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>0.0615</v>
       </c>
       <c r="K48" t="n">
-        <v>95</v>
+        <v>174</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="M48" t="n">
-        <v>0.6233</v>
+        <v>0.4058</v>
       </c>
       <c r="N48" t="n">
-        <v>95</v>
+        <v>229</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>tO0RO</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5336</v>
+        <v>0.5425</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0934</v>
+        <v>0.095</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.3813</v>
+        <v>-0.3715</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5336</v>
+        <v>0.5425</v>
       </c>
       <c r="F49" t="n">
-        <v>0.5336</v>
+        <v>0.6826</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5336</v>
+        <v>0.6826</v>
       </c>
       <c r="I49" t="n">
-        <v>0.5336</v>
+        <v>0.7002</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>0.5336</v>
+        <v>0.7002</v>
       </c>
       <c r="N49" t="n">
-        <v>128</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50">
@@ -2704,16 +2704,16 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5208</v>
+        <v>0.5001</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0912</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.3871</v>
+        <v>-0.3904</v>
       </c>
       <c r="E50" t="n">
-        <v>0.5208</v>
+        <v>0.5001</v>
       </c>
       <c r="F50" t="n">
         <v>0.5208</v>
@@ -2746,47 +2746,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KRIMZ</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5142</v>
+        <v>0.3644</v>
       </c>
       <c r="C51" t="n">
-        <v>0.09</v>
+        <v>0.0638</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.3901</v>
+        <v>-0.4511</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5142</v>
+        <v>0.3644</v>
       </c>
       <c r="F51" t="n">
-        <v>0.8902</v>
+        <v>0.5118</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.376</v>
+        <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8902</v>
+        <v>0.5118</v>
       </c>
       <c r="I51" t="n">
-        <v>0.8902</v>
+        <v>0.5118</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.376</v>
+        <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>145</v>
+        <v>128</v>
       </c>
       <c r="L51" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>0.5142</v>
+        <v>0.5118</v>
       </c>
       <c r="N51" t="n">
-        <v>205</v>
+        <v>128</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5067</v>
+        <v>0.3423</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0887</v>
+        <v>0.0599</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.3935</v>
+        <v>-0.4609</v>
       </c>
       <c r="E52" t="n">
-        <v>0.5067</v>
+        <v>0.3423</v>
       </c>
       <c r="F52" t="n">
-        <v>0.5067</v>
+        <v>0.5243</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.5067</v>
+        <v>0.5243</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5198</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>0.5198</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="N52" t="n">
         <v>238</v>
@@ -2838,216 +2838,216 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>kRaSnaL</t>
+          <t>KRIMZ</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4365</v>
+        <v>0.3329</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0764</v>
+        <v>0.0583</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.4255</v>
+        <v>-0.4651</v>
       </c>
       <c r="E53" t="n">
-        <v>0.4365</v>
+        <v>0.3329</v>
       </c>
       <c r="F53" t="n">
-        <v>0.4365</v>
+        <v>0.9509</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>-0.3663</v>
       </c>
       <c r="H53" t="n">
-        <v>0.4365</v>
+        <v>0.9509</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4365</v>
+        <v>0.9509</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>-0.3663</v>
       </c>
       <c r="K53" t="n">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4365</v>
+        <v>0.5846</v>
       </c>
       <c r="N53" t="n">
-        <v>108</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>esenthial</t>
+          <t>decenty</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-0.0253</v>
+        <v>0.2599</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.0044</v>
+        <v>0.0455</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.6357</v>
+        <v>-0.4977</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.0253</v>
+        <v>0.2599</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.0253</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.0253</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.0253</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.0253</v>
+        <v>-0.08550000000000001</v>
       </c>
       <c r="N54" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>zevy</t>
+          <t>kl1m</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-0.057</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.01</v>
+        <v>0.0113</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.6502</v>
+        <v>-0.5849</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.057</v>
+        <v>0.06469999999999999</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.057</v>
+        <v>-0.1135</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.057</v>
+        <v>-0.1135</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.057</v>
+        <v>-0.1135</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.057</v>
+        <v>-0.1135</v>
       </c>
       <c r="N55" t="n">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Krabeni</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>-0.0664</v>
+        <v>-0.1007</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.0116</v>
+        <v>-0.0176</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.6544</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.0664</v>
+        <v>-0.1007</v>
       </c>
       <c r="F56" t="n">
-        <v>0.86</v>
+        <v>-0.1224</v>
       </c>
       <c r="G56" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.86</v>
+        <v>-0.1224</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8822</v>
+        <v>-0.1224</v>
       </c>
       <c r="J56" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="L56" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.04420000000000002</v>
+        <v>-0.1224</v>
       </c>
       <c r="N56" t="n">
-        <v>260</v>
+        <v>158</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>decenty</t>
+          <t>zevy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-0.0851</v>
+        <v>-0.1197</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.0149</v>
+        <v>-0.021</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.6629</v>
+        <v>-0.6673</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.0851</v>
+        <v>-0.1197</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0851</v>
+        <v>-0.0572</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.0851</v>
+        <v>-0.0572</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.0851</v>
+        <v>-0.0572</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.0851</v>
+        <v>-0.0572</v>
       </c>
       <c r="N57" t="n">
         <v>103</v>
@@ -3068,277 +3068,277 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>kl1m</t>
+          <t>Krabeni</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-0.1135</v>
+        <v>-0.1354</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.0199</v>
+        <v>-0.0237</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6743</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.1135</v>
+        <v>-0.1354</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.1135</v>
+        <v>0.8945</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>-0.9265</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.1135</v>
+        <v>0.8945</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1135</v>
+        <v>0.9176</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>-0.9265</v>
       </c>
       <c r="K58" t="n">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.1135</v>
+        <v>-0.008900000000000019</v>
       </c>
       <c r="N58" t="n">
-        <v>95</v>
+        <v>260</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-0.1229</v>
+        <v>-0.1417</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0215</v>
+        <v>-0.0248</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.6801</v>
+        <v>-0.6771</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1229</v>
+        <v>-0.1417</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.1229</v>
+        <v>-0.2474</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1229</v>
+        <v>-0.2474</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1229</v>
+        <v>-0.2474</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.1229</v>
+        <v>-0.2474</v>
       </c>
       <c r="N59" t="n">
-        <v>158</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>esenthial</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>-0.1503</v>
+        <v>-0.2156</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0263</v>
+        <v>-0.0377</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.6926</v>
+        <v>-0.7101</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.1503</v>
+        <v>-0.2156</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.1503</v>
+        <v>-0.0254</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.1503</v>
+        <v>-0.0254</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1503</v>
+        <v>-0.0254</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>-0.1503</v>
+        <v>-0.0254</v>
       </c>
       <c r="N60" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-0.1896</v>
+        <v>-0.2278</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0332</v>
+        <v>-0.0399</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.7105</v>
+        <v>-0.7156</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.1896</v>
+        <v>-0.2278</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.1896</v>
+        <v>-0.1617</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.1896</v>
+        <v>-0.1617</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.1896</v>
+        <v>-0.1617</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>-0.1896</v>
+        <v>-0.1617</v>
       </c>
       <c r="N61" t="n">
-        <v>83</v>
+        <v>158</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-0.2389</v>
+        <v>-0.3192</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0418</v>
+        <v>-0.0559</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.733</v>
+        <v>-0.7564</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.2389</v>
+        <v>-0.3192</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.2389</v>
+        <v>-0.2707</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>-0.2389</v>
+        <v>-0.2707</v>
       </c>
       <c r="I62" t="n">
-        <v>-0.2389</v>
+        <v>-0.2707</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>-0.2389</v>
+        <v>-0.2707</v>
       </c>
       <c r="N62" t="n">
-        <v>128</v>
+        <v>158</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>xerolte</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-0.2707</v>
+        <v>-0.3265</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.0474</v>
+        <v>-0.0571</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.7474</v>
+        <v>-0.7597</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.2707</v>
+        <v>-0.3265</v>
       </c>
       <c r="F63" t="n">
-        <v>-0.2707</v>
+        <v>-0.427</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.2707</v>
+        <v>-0.427</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.2707</v>
+        <v>-0.427</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>-0.2707</v>
+        <v>-0.427</v>
       </c>
       <c r="N63" t="n">
-        <v>158</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64">
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>-0.3727</v>
+        <v>-0.336</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.0588</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.7939000000000001</v>
+        <v>-0.7639</v>
       </c>
       <c r="E64" t="n">
-        <v>-0.3727</v>
+        <v>-0.336</v>
       </c>
       <c r="F64" t="n">
-        <v>-0.3727</v>
+        <v>-0.3724</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>-0.3727</v>
+        <v>-0.3724</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.3727</v>
+        <v>-0.3724</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>-0.3727</v>
+        <v>-0.3724</v>
       </c>
       <c r="N64" t="n">
         <v>108</v>
@@ -3390,93 +3390,93 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>xerolte</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4818</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0746</v>
+        <v>-0.0843</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.8183</v>
+        <v>-0.829</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4818</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4423</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4423</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4423</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4263</v>
+        <v>-0.4423</v>
       </c>
       <c r="N65" t="n">
-        <v>56</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.4431</v>
+        <v>-0.5105</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0776</v>
+        <v>-0.08939999999999999</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8259</v>
+        <v>-0.8418</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.4431</v>
+        <v>-0.5105</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4431</v>
+        <v>-0.19</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4431</v>
+        <v>-0.19</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.4431</v>
+        <v>-0.19</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="L66" t="n">
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.4431</v>
+        <v>-0.19</v>
       </c>
       <c r="N66" t="n">
-        <v>128</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67">
@@ -3486,28 +3486,28 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.4522</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.0791</v>
+        <v>-0.0975</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-0.8626</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.4522</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.4522</v>
+        <v>-0.4256</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>-0.4522</v>
+        <v>-0.4256</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.4522</v>
+        <v>-0.4256</v>
       </c>
       <c r="J67" t="n">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>-0.4522</v>
+        <v>-0.4256</v>
       </c>
       <c r="N67" t="n">
         <v>103</v>
@@ -3528,400 +3528,400 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>exit</t>
+          <t>sk0R</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8691</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.1036</v>
+        <v>-0.1521</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.8935999999999999</v>
+        <v>-1.002</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8691</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8179</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8179</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8179</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.5917</v>
+        <v>-0.8179</v>
       </c>
       <c r="N68" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>arT</t>
+          <t>hypex</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.6551</v>
+        <v>-0.9064</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.1147</v>
+        <v>-0.1586</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9224</v>
+        <v>-1.0187</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.6551</v>
+        <v>-0.9064</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.6551</v>
+        <v>-0.6938</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.6551</v>
+        <v>-0.6938</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.6551</v>
+        <v>-0.6938</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="L69" t="n">
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.6551</v>
+        <v>-0.6938</v>
       </c>
       <c r="N69" t="n">
-        <v>103</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>hypex</t>
+          <t>exit</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.6933</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.1213</v>
+        <v>-0.1619</v>
       </c>
       <c r="D70" t="n">
-        <v>-0.9398</v>
+        <v>-1.027</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.6933</v>
+        <v>-0.9249000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.6933</v>
+        <v>-0.5917</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.6933</v>
+        <v>-0.5917</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.6933</v>
+        <v>-0.5917</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.6933</v>
+        <v>-0.5917</v>
       </c>
       <c r="N70" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>nin9</t>
+          <t>arT</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-0.7119</v>
+        <v>-0.9881</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.1246</v>
+        <v>-0.1729</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.9483</v>
+        <v>-1.0552</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.7119</v>
+        <v>-0.9881</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.7119</v>
+        <v>-0.6553</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.7119</v>
+        <v>-0.6553</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.7119</v>
+        <v>-0.6553</v>
       </c>
       <c r="J71" t="n">
         <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-0.7119</v>
+        <v>-0.6553</v>
       </c>
       <c r="N71" t="n">
-        <v>56</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Qikert</t>
+          <t>Bart4k</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-0.7199</v>
+        <v>-0.9968</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.126</v>
+        <v>-0.1745</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.9519</v>
+        <v>-1.0591</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.7199</v>
+        <v>-0.9968</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.7199</v>
+        <v>-0.909</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.7199</v>
+        <v>-0.909</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.7199</v>
+        <v>-0.909</v>
       </c>
       <c r="J72" t="n">
         <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>-0.7199</v>
+        <v>-0.909</v>
       </c>
       <c r="N72" t="n">
-        <v>95</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>dgt</t>
+          <t>cobrazera</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-0.8061</v>
+        <v>-1.0211</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.1411</v>
+        <v>-0.1787</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.9912</v>
+        <v>-1.0699</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.8061</v>
+        <v>-1.0211</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.8061</v>
+        <v>-0.876</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
       </c>
       <c r="H73" t="n">
-        <v>-0.8061</v>
+        <v>-0.876</v>
       </c>
       <c r="I73" t="n">
-        <v>-0.8061</v>
+        <v>-0.876</v>
       </c>
       <c r="J73" t="n">
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.8061</v>
+        <v>-0.876</v>
       </c>
       <c r="N73" t="n">
-        <v>130</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sk0R</t>
+          <t>Qikert</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-0.8175</v>
+        <v>-1.0315</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1431</v>
+        <v>-0.1805</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.9963</v>
+        <v>-1.0746</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.8175</v>
+        <v>-1.0315</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.8175</v>
+        <v>-0.7199</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>-0.8175</v>
+        <v>-0.7199</v>
       </c>
       <c r="I74" t="n">
-        <v>-0.8175</v>
+        <v>-0.7199</v>
       </c>
       <c r="J74" t="n">
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.8175</v>
+        <v>-0.7199</v>
       </c>
       <c r="N74" t="n">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>cobrazera</t>
+          <t>dgt</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-0.8756</v>
+        <v>-1.1208</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.1533</v>
+        <v>-0.1962</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.0228</v>
+        <v>-1.1145</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.8756</v>
+        <v>-1.1208</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.8756</v>
+        <v>-0.8061</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-0.8756</v>
+        <v>-0.8061</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.8756</v>
+        <v>-0.8061</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
       </c>
       <c r="K75" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.8756</v>
+        <v>-0.8061</v>
       </c>
       <c r="N75" t="n">
-        <v>56</v>
+        <v>130</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bart4k</t>
+          <t>nin9</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-0.9528</v>
+        <v>-1.141</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.1668</v>
+        <v>-0.1997</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.0579</v>
+        <v>-1.1235</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.9528</v>
+        <v>-1.141</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.9528</v>
+        <v>-0.702</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-0.9528</v>
+        <v>-0.702</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.9528</v>
+        <v>-0.702</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.9528</v>
+        <v>-0.702</v>
       </c>
       <c r="N76" t="n">
         <v>56</v>
@@ -3942,93 +3942,93 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>alex666</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.116</v>
+        <v>-1.4124</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.1953</v>
+        <v>-0.2472</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.1322</v>
+        <v>-1.2447</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.116</v>
+        <v>-1.4124</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.116</v>
+        <v>-1.2805</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.116</v>
+        <v>-1.2805</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.116</v>
+        <v>-1.2805</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.116</v>
+        <v>-1.2805</v>
       </c>
       <c r="N77" t="n">
-        <v>108</v>
+        <v>128</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>alex666</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.2811</v>
+        <v>-1.4594</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.2242</v>
+        <v>-0.2554</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.2074</v>
+        <v>-1.2657</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.2811</v>
+        <v>-1.4594</v>
       </c>
       <c r="F78" t="n">
-        <v>-1.2811</v>
+        <v>-1.116</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.2811</v>
+        <v>-1.116</v>
       </c>
       <c r="I78" t="n">
-        <v>-1.2811</v>
+        <v>-1.116</v>
       </c>
       <c r="J78" t="n">
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
       </c>
       <c r="M78" t="n">
-        <v>-1.2811</v>
+        <v>-1.116</v>
       </c>
       <c r="N78" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79">
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-1.3531</v>
+        <v>-1.6296</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.2368</v>
+        <v>-0.2852</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.2402</v>
+        <v>-1.3417</v>
       </c>
       <c r="E79" t="n">
-        <v>-1.3531</v>
+        <v>-1.6296</v>
       </c>
       <c r="F79" t="n">
-        <v>-1.3531</v>
+        <v>-1.3683</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-1.3531</v>
+        <v>-1.3683</v>
       </c>
       <c r="I79" t="n">
-        <v>-1.388</v>
+        <v>-1.4036</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-1.388</v>
+        <v>-1.4036</v>
       </c>
       <c r="N79" t="n">
         <v>238</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-1.5662</v>
+        <v>-1.6874</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.2741</v>
+        <v>-0.2953</v>
       </c>
       <c r="D80" t="n">
-        <v>-1.3372</v>
+        <v>-1.3675</v>
       </c>
       <c r="E80" t="n">
-        <v>-1.5662</v>
+        <v>-1.6874</v>
       </c>
       <c r="F80" t="n">
         <v>-1.5662</v>
@@ -4126,35 +4126,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-2.1958</v>
+        <v>-2.5448</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.3843</v>
+        <v>-0.4454</v>
       </c>
       <c r="D81" t="n">
-        <v>-1.6238</v>
+        <v>-1.7505</v>
       </c>
       <c r="E81" t="n">
-        <v>-2.1958</v>
+        <v>-2.5448</v>
       </c>
       <c r="F81" t="n">
-        <v>-2.117</v>
+        <v>-2.1095</v>
       </c>
       <c r="G81" t="n">
-        <v>-0.0788</v>
+        <v>-0.0793</v>
       </c>
       <c r="H81" t="n">
-        <v>-2.117</v>
+        <v>-2.1095</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.117</v>
+        <v>-2.1095</v>
       </c>
       <c r="J81" t="n">
-        <v>-0.0788</v>
+        <v>-0.0793</v>
       </c>
       <c r="K81" t="n">
         <v>145</v>
@@ -4163,7 +4163,7 @@
         <v>60</v>
       </c>
       <c r="M81" t="n">
-        <v>-2.1958</v>
+        <v>-2.1888</v>
       </c>
       <c r="N81" t="n">
         <v>205</v>
@@ -4269,10 +4269,10 @@
         <v>0.99</v>
       </c>
       <c r="I2" t="n">
-        <v>0.012</v>
+        <v>0.0113</v>
       </c>
       <c r="J2" t="n">
-        <v>0.228</v>
+        <v>0.2147</v>
       </c>
     </row>
     <row r="3">
@@ -4309,10 +4309,10 @@
         <v>0.77</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2591</v>
+        <v>-0.2593</v>
       </c>
       <c r="J3" t="n">
-        <v>-4.9229</v>
+        <v>-4.9267</v>
       </c>
     </row>
     <row r="4">
@@ -4349,10 +4349,10 @@
         <v>0.76</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2683</v>
+        <v>-0.2684</v>
       </c>
       <c r="J4" t="n">
-        <v>-5.0977</v>
+        <v>-5.0996</v>
       </c>
     </row>
     <row r="5">
@@ -4386,13 +4386,13 @@
         <v>19</v>
       </c>
       <c r="H5" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3768</v>
+        <v>-0.368</v>
       </c>
       <c r="J5" t="n">
-        <v>-7.1592</v>
+        <v>-6.992</v>
       </c>
     </row>
     <row r="6">
@@ -4429,10 +4429,10 @@
         <v>0.61</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4036</v>
+        <v>-0.4039</v>
       </c>
       <c r="J6" t="n">
-        <v>-7.6684</v>
+        <v>-7.6741</v>
       </c>
     </row>
     <row r="7">
@@ -4669,10 +4669,10 @@
         <v>1.53</v>
       </c>
       <c r="I12" t="n">
-        <v>0.702</v>
+        <v>0.7015</v>
       </c>
       <c r="J12" t="n">
-        <v>16.848</v>
+        <v>16.836</v>
       </c>
     </row>
     <row r="13">
@@ -4706,13 +4706,13 @@
         <v>24</v>
       </c>
       <c r="H13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1588</v>
+        <v>0.1737</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8112</v>
+        <v>4.1688</v>
       </c>
     </row>
     <row r="14">
@@ -4749,10 +4749,10 @@
         <v>0.93</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.1109</v>
+        <v>-0.111</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.6616</v>
+        <v>-2.664</v>
       </c>
     </row>
     <row r="15">
@@ -4789,10 +4789,10 @@
         <v>0.86</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1902</v>
+        <v>-0.1904</v>
       </c>
       <c r="J15" t="n">
-        <v>-4.5648</v>
+        <v>-4.5696</v>
       </c>
     </row>
     <row r="16">
@@ -4829,10 +4829,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4713</v>
+        <v>-0.4714</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.3112</v>
+        <v>-11.3136</v>
       </c>
     </row>
     <row r="17">
@@ -4869,10 +4869,10 @@
         <v>1.26</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4174</v>
+        <v>0.4178</v>
       </c>
       <c r="J17" t="n">
-        <v>10.0176</v>
+        <v>10.0272</v>
       </c>
     </row>
     <row r="18">
@@ -4906,13 +4906,13 @@
         <v>24</v>
       </c>
       <c r="H18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1498</v>
+        <v>0.1333</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5952</v>
+        <v>3.1992</v>
       </c>
     </row>
     <row r="19">
@@ -4949,10 +4949,10 @@
         <v>0.93</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1117</v>
+        <v>-0.1115</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.6808</v>
+        <v>-2.676</v>
       </c>
     </row>
     <row r="20">
@@ -4989,10 +4989,10 @@
         <v>0.88</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1695</v>
+        <v>-0.1693</v>
       </c>
       <c r="J20" t="n">
-        <v>-4.068</v>
+        <v>-4.0632</v>
       </c>
     </row>
     <row r="21">
@@ -5029,10 +5029,10 @@
         <v>0.87</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1804</v>
+        <v>-0.1802</v>
       </c>
       <c r="J21" t="n">
-        <v>-4.3296</v>
+        <v>-4.3248</v>
       </c>
     </row>
     <row r="22">
@@ -5466,13 +5466,13 @@
         <v>23</v>
       </c>
       <c r="H32" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="I32" t="n">
-        <v>0.573</v>
+        <v>0.5885</v>
       </c>
       <c r="J32" t="n">
-        <v>13.179</v>
+        <v>13.5355</v>
       </c>
     </row>
     <row r="33">
@@ -5509,10 +5509,10 @@
         <v>1.22</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4741</v>
+        <v>0.4736</v>
       </c>
       <c r="J33" t="n">
-        <v>10.9043</v>
+        <v>10.8928</v>
       </c>
     </row>
     <row r="34">
@@ -5549,10 +5549,10 @@
         <v>0.89</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.156</v>
+        <v>-0.1561</v>
       </c>
       <c r="J34" t="n">
-        <v>-3.588</v>
+        <v>-3.5903</v>
       </c>
     </row>
     <row r="35">
@@ -5589,10 +5589,10 @@
         <v>0.86</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1886</v>
+        <v>-0.1888</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.3378</v>
+        <v>-4.3424</v>
       </c>
     </row>
     <row r="36">
@@ -5629,10 +5629,10 @@
         <v>0.62</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4174</v>
+        <v>-0.4176</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.600199999999999</v>
+        <v>-9.604799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -9266,13 +9266,13 @@
         <v>21</v>
       </c>
       <c r="H127" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7098</v>
+        <v>0.7244</v>
       </c>
       <c r="J127" t="n">
-        <v>14.9058</v>
+        <v>15.2124</v>
       </c>
     </row>
     <row r="128">
@@ -9309,10 +9309,10 @@
         <v>1.27</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6333</v>
       </c>
       <c r="J128" t="n">
-        <v>13.3056</v>
+        <v>13.2993</v>
       </c>
     </row>
     <row r="129">
@@ -9349,10 +9349,10 @@
         <v>1.26</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6181</v>
+        <v>0.6177</v>
       </c>
       <c r="J129" t="n">
-        <v>12.9801</v>
+        <v>12.9717</v>
       </c>
     </row>
     <row r="130">
@@ -9389,10 +9389,10 @@
         <v>0.98</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.1252</v>
+        <v>-0.1255</v>
       </c>
       <c r="J130" t="n">
-        <v>-2.6292</v>
+        <v>-2.6355</v>
       </c>
     </row>
     <row r="131">
@@ -9429,10 +9429,10 @@
         <v>0.9</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.3704</v>
+        <v>-0.3708</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.7784</v>
+        <v>-7.7868</v>
       </c>
     </row>
     <row r="132">
@@ -10069,10 +10069,10 @@
         <v>1.15</v>
       </c>
       <c r="I147" t="n">
-        <v>0.3524</v>
+        <v>0.3519</v>
       </c>
       <c r="J147" t="n">
-        <v>12.334</v>
+        <v>12.3165</v>
       </c>
     </row>
     <row r="148">
@@ -10109,16 +10109,16 @@
         <v>1.14</v>
       </c>
       <c r="I148" t="n">
-        <v>0.3341</v>
+        <v>0.3336</v>
       </c>
       <c r="J148" t="n">
-        <v>11.6935</v>
+        <v>11.676</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>lauNX</t>
+          <t>dem0n</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -10149,16 +10149,16 @@
         <v>1.01</v>
       </c>
       <c r="I149" t="n">
-        <v>0.0466</v>
+        <v>0.0464</v>
       </c>
       <c r="J149" t="n">
-        <v>1.631</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>dem0n</t>
+          <t>lauNX</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -10186,13 +10186,13 @@
         <v>35</v>
       </c>
       <c r="H150" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I150" t="n">
-        <v>0.0027</v>
+        <v>0.0464</v>
       </c>
       <c r="J150" t="n">
-        <v>0.0945</v>
+        <v>1.624</v>
       </c>
     </row>
     <row r="151">
@@ -10229,10 +10229,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4697</v>
+        <v>-0.4698</v>
       </c>
       <c r="J151" t="n">
-        <v>-16.4395</v>
+        <v>-16.443</v>
       </c>
     </row>
     <row r="152">
@@ -10798,7 +10798,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11158,7 +11158,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11438,7 +11438,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11469,10 +11469,10 @@
         <v>1.2</v>
       </c>
       <c r="I182" t="n">
-        <v>0.4524</v>
+        <v>0.4519</v>
       </c>
       <c r="J182" t="n">
-        <v>9.9528</v>
+        <v>9.941800000000001</v>
       </c>
     </row>
     <row r="183">
@@ -11509,10 +11509,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0183</v>
+        <v>-0.0186</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.4026</v>
+        <v>-0.4092</v>
       </c>
     </row>
     <row r="184">
@@ -11549,10 +11549,10 @@
         <v>0.9</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.1398</v>
+        <v>-0.1399</v>
       </c>
       <c r="J184" t="n">
-        <v>-3.0756</v>
+        <v>-3.0778</v>
       </c>
     </row>
     <row r="185">
@@ -11586,13 +11586,13 @@
         <v>22</v>
       </c>
       <c r="H185" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.2538</v>
+        <v>-0.2441</v>
       </c>
       <c r="J185" t="n">
-        <v>-5.5836</v>
+        <v>-5.3702</v>
       </c>
     </row>
     <row r="186">
@@ -11629,10 +11629,10 @@
         <v>0.67</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.3667</v>
+        <v>-0.3669</v>
       </c>
       <c r="J186" t="n">
-        <v>-8.067399999999999</v>
+        <v>-8.0718</v>
       </c>
     </row>
     <row r="187">
@@ -11869,10 +11869,10 @@
         <v>1.47</v>
       </c>
       <c r="I192" t="n">
-        <v>0.5966</v>
+        <v>0.5959</v>
       </c>
       <c r="J192" t="n">
-        <v>13.1252</v>
+        <v>13.1098</v>
       </c>
     </row>
     <row r="193">
@@ -11906,13 +11906,13 @@
         <v>22</v>
       </c>
       <c r="H193" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="I193" t="n">
-        <v>0.3809</v>
+        <v>0.403</v>
       </c>
       <c r="J193" t="n">
-        <v>8.379799999999999</v>
+        <v>8.866</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>1.22</v>
       </c>
       <c r="I194" t="n">
-        <v>0.3233</v>
+        <v>0.323</v>
       </c>
       <c r="J194" t="n">
-        <v>7.1126</v>
+        <v>7.106</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.99</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.0391</v>
+        <v>-0.0394</v>
       </c>
       <c r="J195" t="n">
-        <v>-0.8602</v>
+        <v>-0.8668</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.98</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.0569</v>
+        <v>-0.0572</v>
       </c>
       <c r="J196" t="n">
-        <v>-1.2518</v>
+        <v>-1.2584</v>
       </c>
     </row>
     <row r="197">
@@ -12518,7 +12518,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12558,7 +12558,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13466,13 +13466,13 @@
         <v>24</v>
       </c>
       <c r="H232" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I232" t="n">
-        <v>0.6887</v>
+        <v>0.6973</v>
       </c>
       <c r="J232" t="n">
-        <v>16.5288</v>
+        <v>16.7352</v>
       </c>
     </row>
     <row r="233">
@@ -13506,13 +13506,13 @@
         <v>24</v>
       </c>
       <c r="H233" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="I233" t="n">
-        <v>0.1758</v>
+        <v>0.2048</v>
       </c>
       <c r="J233" t="n">
-        <v>4.2192</v>
+        <v>4.9152</v>
       </c>
     </row>
     <row r="234">
@@ -13546,13 +13546,13 @@
         <v>24</v>
       </c>
       <c r="H234" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I234" t="n">
-        <v>0.0743</v>
+        <v>0.0926</v>
       </c>
       <c r="J234" t="n">
-        <v>1.7832</v>
+        <v>2.2224</v>
       </c>
     </row>
     <row r="235">
@@ -13586,13 +13586,13 @@
         <v>24</v>
       </c>
       <c r="H235" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="I235" t="n">
-        <v>0.0535</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="J235" t="n">
-        <v>1.284</v>
+        <v>1.7616</v>
       </c>
     </row>
     <row r="236">
@@ -13629,10 +13629,10 @@
         <v>0.64</v>
       </c>
       <c r="I236" t="n">
-        <v>-0.4065</v>
+        <v>-0.4072</v>
       </c>
       <c r="J236" t="n">
-        <v>-9.756</v>
+        <v>-9.7728</v>
       </c>
     </row>
     <row r="237">
@@ -13666,19 +13666,19 @@
         <v>24</v>
       </c>
       <c r="H237" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="I237" t="n">
-        <v>0.4872</v>
+        <v>0.4771</v>
       </c>
       <c r="J237" t="n">
-        <v>11.6928</v>
+        <v>11.4504</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>broky</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -13706,19 +13706,19 @@
         <v>24</v>
       </c>
       <c r="H238" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I238" t="n">
-        <v>0.2915</v>
+        <v>0.2797</v>
       </c>
       <c r="J238" t="n">
-        <v>6.996</v>
+        <v>6.7128</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>broky</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -13746,13 +13746,13 @@
         <v>24</v>
       </c>
       <c r="H239" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I239" t="n">
-        <v>0.2792</v>
+        <v>0.2673</v>
       </c>
       <c r="J239" t="n">
-        <v>6.7008</v>
+        <v>6.4152</v>
       </c>
     </row>
     <row r="240">
@@ -13786,13 +13786,13 @@
         <v>24</v>
       </c>
       <c r="H240" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I240" t="n">
-        <v>-0.0532</v>
+        <v>-0.0349</v>
       </c>
       <c r="J240" t="n">
-        <v>-1.2768</v>
+        <v>-0.8376</v>
       </c>
     </row>
     <row r="241">
@@ -13826,13 +13826,13 @@
         <v>24</v>
       </c>
       <c r="H241" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="I241" t="n">
-        <v>-0.0532</v>
+        <v>-0.0684</v>
       </c>
       <c r="J241" t="n">
-        <v>-1.2768</v>
+        <v>-1.6416</v>
       </c>
     </row>
     <row r="242">
@@ -14069,10 +14069,10 @@
         <v>1.19</v>
       </c>
       <c r="I247" t="n">
-        <v>0.427</v>
+        <v>0.4275</v>
       </c>
       <c r="J247" t="n">
-        <v>9.821</v>
+        <v>9.8325</v>
       </c>
     </row>
     <row r="248">
@@ -14106,13 +14106,13 @@
         <v>23</v>
       </c>
       <c r="H248" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="I248" t="n">
-        <v>0.2408</v>
+        <v>0.2206</v>
       </c>
       <c r="J248" t="n">
-        <v>5.5384</v>
+        <v>5.0738</v>
       </c>
     </row>
     <row r="249">
@@ -14149,10 +14149,10 @@
         <v>1</v>
       </c>
       <c r="I249" t="n">
-        <v>0.0046</v>
+        <v>0.0049</v>
       </c>
       <c r="J249" t="n">
-        <v>0.1058</v>
+        <v>0.1127</v>
       </c>
     </row>
     <row r="250">
@@ -14189,10 +14189,10 @@
         <v>0.86</v>
       </c>
       <c r="I250" t="n">
-        <v>-0.1871</v>
+        <v>-0.187</v>
       </c>
       <c r="J250" t="n">
-        <v>-4.3033</v>
+        <v>-4.301</v>
       </c>
     </row>
     <row r="251">
@@ -14229,10 +14229,10 @@
         <v>0.65</v>
       </c>
       <c r="I251" t="n">
-        <v>-0.3893</v>
+        <v>-0.3891</v>
       </c>
       <c r="J251" t="n">
-        <v>-8.953900000000001</v>
+        <v>-8.949299999999999</v>
       </c>
     </row>
     <row r="252">
@@ -14269,10 +14269,10 @@
         <v>1.04</v>
       </c>
       <c r="I252" t="n">
-        <v>0.2343</v>
+        <v>0.232</v>
       </c>
       <c r="J252" t="n">
-        <v>3.7488</v>
+        <v>3.712</v>
       </c>
     </row>
     <row r="253">
@@ -14309,10 +14309,10 @@
         <v>0.68</v>
       </c>
       <c r="I253" t="n">
-        <v>-0.3322</v>
+        <v>-0.3326</v>
       </c>
       <c r="J253" t="n">
-        <v>-5.3152</v>
+        <v>-5.3216</v>
       </c>
     </row>
     <row r="254">
@@ -14349,10 +14349,10 @@
         <v>0.59</v>
       </c>
       <c r="I254" t="n">
-        <v>-0.4102</v>
+        <v>-0.4108</v>
       </c>
       <c r="J254" t="n">
-        <v>-6.5632</v>
+        <v>-6.5728</v>
       </c>
     </row>
     <row r="255">
@@ -14386,19 +14386,19 @@
         <v>16</v>
       </c>
       <c r="H255" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I255" t="n">
-        <v>-0.4455</v>
+        <v>-0.4373</v>
       </c>
       <c r="J255" t="n">
-        <v>-7.128</v>
+        <v>-6.9968</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -14426,13 +14426,13 @@
         <v>16</v>
       </c>
       <c r="H256" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="I256" t="n">
-        <v>-0.5159</v>
+        <v>-0.5077</v>
       </c>
       <c r="J256" t="n">
-        <v>-8.2544</v>
+        <v>-8.123200000000001</v>
       </c>
     </row>
     <row r="257">
@@ -14469,10 +14469,10 @@
         <v>2.03</v>
       </c>
       <c r="I257" t="n">
-        <v>1.7137</v>
+        <v>1.7178</v>
       </c>
       <c r="J257" t="n">
-        <v>27.4192</v>
+        <v>27.4848</v>
       </c>
     </row>
     <row r="258">
@@ -14506,13 +14506,13 @@
         <v>16</v>
       </c>
       <c r="H258" t="n">
-        <v>1.67</v>
+        <v>1.58</v>
       </c>
       <c r="I258" t="n">
-        <v>1.2816</v>
+        <v>1.1709</v>
       </c>
       <c r="J258" t="n">
-        <v>20.5056</v>
+        <v>18.7344</v>
       </c>
     </row>
     <row r="259">
@@ -14546,13 +14546,13 @@
         <v>16</v>
       </c>
       <c r="H259" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="I259" t="n">
-        <v>1.066</v>
+        <v>1.081</v>
       </c>
       <c r="J259" t="n">
-        <v>17.056</v>
+        <v>17.296</v>
       </c>
     </row>
     <row r="260">
@@ -14586,13 +14586,13 @@
         <v>16</v>
       </c>
       <c r="H260" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="I260" t="n">
-        <v>0.1599</v>
+        <v>0.1323</v>
       </c>
       <c r="J260" t="n">
-        <v>2.5584</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="261">
@@ -14629,10 +14629,10 @@
         <v>0.99</v>
       </c>
       <c r="I261" t="n">
-        <v>-0.133</v>
+        <v>-0.1305</v>
       </c>
       <c r="J261" t="n">
-        <v>-2.128</v>
+        <v>-2.088</v>
       </c>
     </row>
     <row r="262">
@@ -14798,7 +14798,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -15118,7 +15118,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -16666,13 +16666,13 @@
         <v>22</v>
       </c>
       <c r="H312" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="I312" t="n">
-        <v>0.476</v>
+        <v>0.4874</v>
       </c>
       <c r="J312" t="n">
-        <v>10.472</v>
+        <v>10.7228</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.28</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4169</v>
+        <v>0.4167</v>
       </c>
       <c r="J313" t="n">
-        <v>9.171799999999999</v>
+        <v>9.167400000000001</v>
       </c>
     </row>
     <row r="314">
@@ -16749,10 +16749,10 @@
         <v>1.21</v>
       </c>
       <c r="I314" t="n">
-        <v>0.331</v>
+        <v>0.3308</v>
       </c>
       <c r="J314" t="n">
-        <v>7.282</v>
+        <v>7.2776</v>
       </c>
     </row>
     <row r="315">
@@ -16789,10 +16789,10 @@
         <v>1.01</v>
       </c>
       <c r="I315" t="n">
-        <v>0.0197</v>
+        <v>0.0195</v>
       </c>
       <c r="J315" t="n">
-        <v>0.4334</v>
+        <v>0.429</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.95</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.09859999999999999</v>
+        <v>-0.0987</v>
       </c>
       <c r="J316" t="n">
-        <v>-2.1692</v>
+        <v>-2.1714</v>
       </c>
     </row>
     <row r="317">
@@ -16869,10 +16869,10 @@
         <v>1.44</v>
       </c>
       <c r="I317" t="n">
-        <v>0.5875</v>
+        <v>0.5879</v>
       </c>
       <c r="J317" t="n">
-        <v>12.925</v>
+        <v>12.9338</v>
       </c>
     </row>
     <row r="318">
@@ -16909,10 +16909,10 @@
         <v>1.04</v>
       </c>
       <c r="I318" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.0882</v>
       </c>
       <c r="J318" t="n">
-        <v>1.936</v>
+        <v>1.9404</v>
       </c>
     </row>
     <row r="319">
@@ -16949,10 +16949,10 @@
         <v>0.99</v>
       </c>
       <c r="I319" t="n">
-        <v>-0.0296</v>
+        <v>-0.0295</v>
       </c>
       <c r="J319" t="n">
-        <v>-0.6512</v>
+        <v>-0.649</v>
       </c>
     </row>
     <row r="320">
@@ -16989,10 +16989,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I320" t="n">
-        <v>-0.1042</v>
+        <v>-0.1041</v>
       </c>
       <c r="J320" t="n">
-        <v>-2.2924</v>
+        <v>-2.2902</v>
       </c>
     </row>
     <row r="321">
@@ -17026,13 +17026,13 @@
         <v>22</v>
       </c>
       <c r="H321" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="I321" t="n">
-        <v>-0.1408</v>
+        <v>-0.1523</v>
       </c>
       <c r="J321" t="n">
-        <v>-3.0976</v>
+        <v>-3.3506</v>
       </c>
     </row>
     <row r="322">
@@ -18266,13 +18266,13 @@
         <v>19</v>
       </c>
       <c r="H352" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="I352" t="n">
-        <v>0.6742</v>
+        <v>0.6582</v>
       </c>
       <c r="J352" t="n">
-        <v>12.8098</v>
+        <v>12.5058</v>
       </c>
     </row>
     <row r="353">
@@ -18346,13 +18346,13 @@
         <v>19</v>
       </c>
       <c r="H354" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="I354" t="n">
-        <v>-0.0522</v>
+        <v>-0.0364</v>
       </c>
       <c r="J354" t="n">
-        <v>-0.9918</v>
+        <v>-0.6916</v>
       </c>
     </row>
     <row r="355">
@@ -18469,10 +18469,10 @@
         <v>1.79</v>
       </c>
       <c r="I357" t="n">
-        <v>1.4454</v>
+        <v>1.4458</v>
       </c>
       <c r="J357" t="n">
-        <v>27.4626</v>
+        <v>27.4702</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.68</v>
       </c>
       <c r="I358" t="n">
-        <v>1.3082</v>
+        <v>1.3086</v>
       </c>
       <c r="J358" t="n">
-        <v>24.8558</v>
+        <v>24.8634</v>
       </c>
     </row>
     <row r="359">
@@ -18546,13 +18546,13 @@
         <v>19</v>
       </c>
       <c r="H359" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="I359" t="n">
-        <v>1.0039</v>
+        <v>0.9883999999999999</v>
       </c>
       <c r="J359" t="n">
-        <v>19.0741</v>
+        <v>18.7796</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.01</v>
       </c>
       <c r="I360" t="n">
-        <v>-0.0008</v>
+        <v>-0.0005</v>
       </c>
       <c r="J360" t="n">
-        <v>-0.0152</v>
+        <v>-0.0095</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>0.89</v>
       </c>
       <c r="I361" t="n">
-        <v>-0.4327</v>
+        <v>-0.4324</v>
       </c>
       <c r="J361" t="n">
-        <v>-8.221299999999999</v>
+        <v>-8.2156</v>
       </c>
     </row>
     <row r="362">
@@ -18678,7 +18678,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -18866,13 +18866,13 @@
         <v>29</v>
       </c>
       <c r="H367" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I367" t="n">
-        <v>0.6593</v>
+        <v>0.68</v>
       </c>
       <c r="J367" t="n">
-        <v>19.1197</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="368">
@@ -18909,10 +18909,10 @@
         <v>1.19</v>
       </c>
       <c r="I368" t="n">
-        <v>0.5294</v>
+        <v>0.5291</v>
       </c>
       <c r="J368" t="n">
-        <v>15.3526</v>
+        <v>15.3439</v>
       </c>
     </row>
     <row r="369">
@@ -18949,10 +18949,10 @@
         <v>1.17</v>
       </c>
       <c r="I369" t="n">
-        <v>0.4847</v>
+        <v>0.4844</v>
       </c>
       <c r="J369" t="n">
-        <v>14.0563</v>
+        <v>14.0476</v>
       </c>
     </row>
     <row r="370">
@@ -18989,10 +18989,10 @@
         <v>1.12</v>
       </c>
       <c r="I370" t="n">
-        <v>0.3685</v>
+        <v>0.3682</v>
       </c>
       <c r="J370" t="n">
-        <v>10.6865</v>
+        <v>10.6778</v>
       </c>
     </row>
     <row r="371">
@@ -19029,10 +19029,10 @@
         <v>1.02</v>
       </c>
       <c r="I371" t="n">
-        <v>0.0764</v>
+        <v>0.0761</v>
       </c>
       <c r="J371" t="n">
-        <v>2.2156</v>
+        <v>2.2069</v>
       </c>
     </row>
     <row r="372">
@@ -19198,7 +19198,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -19469,10 +19469,10 @@
         <v>1.65</v>
       </c>
       <c r="I382" t="n">
-        <v>1.2876</v>
+        <v>1.2867</v>
       </c>
       <c r="J382" t="n">
-        <v>23.1768</v>
+        <v>23.1606</v>
       </c>
     </row>
     <row r="383">
@@ -19506,13 +19506,13 @@
         <v>18</v>
       </c>
       <c r="H383" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="I383" t="n">
-        <v>1.1961</v>
+        <v>1.2216</v>
       </c>
       <c r="J383" t="n">
-        <v>21.5298</v>
+        <v>21.9888</v>
       </c>
     </row>
     <row r="384">
@@ -19549,10 +19549,10 @@
         <v>1.38</v>
       </c>
       <c r="I384" t="n">
-        <v>0.8958</v>
+        <v>0.8951</v>
       </c>
       <c r="J384" t="n">
-        <v>16.1244</v>
+        <v>16.1118</v>
       </c>
     </row>
     <row r="385">
@@ -19589,10 +19589,10 @@
         <v>0.96</v>
       </c>
       <c r="I385" t="n">
-        <v>-0.2183</v>
+        <v>-0.219</v>
       </c>
       <c r="J385" t="n">
-        <v>-3.9294</v>
+        <v>-3.942</v>
       </c>
     </row>
     <row r="386">
@@ -19629,10 +19629,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I386" t="n">
-        <v>-0.6145</v>
+        <v>-0.6151</v>
       </c>
       <c r="J386" t="n">
-        <v>-11.061</v>
+        <v>-11.0718</v>
       </c>
     </row>
     <row r="387">
@@ -20269,10 +20269,10 @@
         <v>1.55</v>
       </c>
       <c r="I402" t="n">
-        <v>1.209</v>
+        <v>1.2083</v>
       </c>
       <c r="J402" t="n">
-        <v>36.27</v>
+        <v>36.249</v>
       </c>
     </row>
     <row r="403">
@@ -20309,10 +20309,10 @@
         <v>1.38</v>
       </c>
       <c r="I403" t="n">
-        <v>0.9486</v>
+        <v>0.9479</v>
       </c>
       <c r="J403" t="n">
-        <v>28.458</v>
+        <v>28.437</v>
       </c>
     </row>
     <row r="404">
@@ -20346,13 +20346,13 @@
         <v>30</v>
       </c>
       <c r="H404" t="n">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="I404" t="n">
-        <v>-0.1109</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J404" t="n">
-        <v>-3.327</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="405">
@@ -20389,16 +20389,16 @@
         <v>0.85</v>
       </c>
       <c r="I405" t="n">
-        <v>-0.4828</v>
+        <v>-0.4832</v>
       </c>
       <c r="J405" t="n">
-        <v>-14.484</v>
+        <v>-14.496</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -20429,10 +20429,10 @@
         <v>0.58</v>
       </c>
       <c r="I406" t="n">
-        <v>-1.0699</v>
+        <v>-1.0703</v>
       </c>
       <c r="J406" t="n">
-        <v>-32.097</v>
+        <v>-32.109</v>
       </c>
     </row>
     <row r="407">
@@ -20669,10 +20669,10 @@
         <v>1.51</v>
       </c>
       <c r="I412" t="n">
-        <v>1.1359</v>
+        <v>1.1354</v>
       </c>
       <c r="J412" t="n">
-        <v>26.1257</v>
+        <v>26.1142</v>
       </c>
     </row>
     <row r="413">
@@ -20709,10 +20709,10 @@
         <v>1.23</v>
       </c>
       <c r="I413" t="n">
-        <v>0.6215000000000001</v>
+        <v>0.621</v>
       </c>
       <c r="J413" t="n">
-        <v>14.2945</v>
+        <v>14.283</v>
       </c>
     </row>
     <row r="414">
@@ -20749,10 +20749,10 @@
         <v>1.21</v>
       </c>
       <c r="I414" t="n">
-        <v>0.5778</v>
+        <v>0.5774</v>
       </c>
       <c r="J414" t="n">
-        <v>13.2894</v>
+        <v>13.2802</v>
       </c>
     </row>
     <row r="415">
@@ -20786,19 +20786,19 @@
         <v>23</v>
       </c>
       <c r="H415" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I415" t="n">
-        <v>0.5109</v>
+        <v>0.533</v>
       </c>
       <c r="J415" t="n">
-        <v>11.7507</v>
+        <v>12.259</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -20829,10 +20829,10 @@
         <v>0.5</v>
       </c>
       <c r="I416" t="n">
-        <v>-1.2359</v>
+        <v>-1.2362</v>
       </c>
       <c r="J416" t="n">
-        <v>-28.4257</v>
+        <v>-28.4326</v>
       </c>
     </row>
     <row r="417">
@@ -20869,10 +20869,10 @@
         <v>1.32</v>
       </c>
       <c r="I417" t="n">
-        <v>0.6459</v>
+        <v>0.6452</v>
       </c>
       <c r="J417" t="n">
-        <v>14.8557</v>
+        <v>14.8396</v>
       </c>
     </row>
     <row r="418">
@@ -20909,10 +20909,10 @@
         <v>1.12</v>
       </c>
       <c r="I418" t="n">
-        <v>0.3025</v>
+        <v>0.3021</v>
       </c>
       <c r="J418" t="n">
-        <v>6.9575</v>
+        <v>6.9483</v>
       </c>
     </row>
     <row r="419">
@@ -20946,13 +20946,13 @@
         <v>23</v>
       </c>
       <c r="H419" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="I419" t="n">
-        <v>0.1083</v>
+        <v>0.133</v>
       </c>
       <c r="J419" t="n">
-        <v>2.4909</v>
+        <v>3.059</v>
       </c>
     </row>
     <row r="420">
@@ -20989,10 +20989,10 @@
         <v>0.66</v>
       </c>
       <c r="I420" t="n">
-        <v>-0.3792</v>
+        <v>-0.3794</v>
       </c>
       <c r="J420" t="n">
-        <v>-8.7216</v>
+        <v>-8.7262</v>
       </c>
     </row>
     <row r="421">
@@ -21029,10 +21029,10 @@
         <v>0.6</v>
       </c>
       <c r="I421" t="n">
-        <v>-0.4326</v>
+        <v>-0.4328</v>
       </c>
       <c r="J421" t="n">
-        <v>-9.9498</v>
+        <v>-9.9544</v>
       </c>
     </row>
     <row r="422">
@@ -21066,13 +21066,13 @@
         <v>19</v>
       </c>
       <c r="H422" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I422" t="n">
-        <v>0.4474</v>
+        <v>0.4632</v>
       </c>
       <c r="J422" t="n">
-        <v>8.5006</v>
+        <v>8.800800000000001</v>
       </c>
     </row>
     <row r="423">
@@ -21106,13 +21106,13 @@
         <v>19</v>
       </c>
       <c r="H423" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I423" t="n">
-        <v>0.3612</v>
+        <v>0.378</v>
       </c>
       <c r="J423" t="n">
-        <v>6.8628</v>
+        <v>7.182</v>
       </c>
     </row>
     <row r="424">
@@ -21149,10 +21149,10 @@
         <v>1.12</v>
       </c>
       <c r="I424" t="n">
-        <v>0.2883</v>
+        <v>0.2876</v>
       </c>
       <c r="J424" t="n">
-        <v>5.4777</v>
+        <v>5.4644</v>
       </c>
     </row>
     <row r="425">
@@ -21189,10 +21189,10 @@
         <v>0.95</v>
       </c>
       <c r="I425" t="n">
-        <v>-0.0871</v>
+        <v>-0.08749999999999999</v>
       </c>
       <c r="J425" t="n">
-        <v>-1.6549</v>
+        <v>-1.6625</v>
       </c>
     </row>
     <row r="426">
@@ -21229,10 +21229,10 @@
         <v>0.63</v>
       </c>
       <c r="I426" t="n">
-        <v>-0.412</v>
+        <v>-0.4123</v>
       </c>
       <c r="J426" t="n">
-        <v>-7.828</v>
+        <v>-7.8337</v>
       </c>
     </row>
     <row r="427">
@@ -21269,10 +21269,10 @@
         <v>1.66</v>
       </c>
       <c r="I427" t="n">
-        <v>1.3014</v>
+        <v>1.3018</v>
       </c>
       <c r="J427" t="n">
-        <v>24.7266</v>
+        <v>24.7342</v>
       </c>
     </row>
     <row r="428">
@@ -21306,13 +21306,13 @@
         <v>19</v>
       </c>
       <c r="H428" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="I428" t="n">
-        <v>0.7612</v>
+        <v>0.7418</v>
       </c>
       <c r="J428" t="n">
-        <v>14.4628</v>
+        <v>14.0942</v>
       </c>
     </row>
     <row r="429">
@@ -21349,10 +21349,10 @@
         <v>1.28</v>
       </c>
       <c r="I429" t="n">
-        <v>0.7022</v>
+        <v>0.7024</v>
       </c>
       <c r="J429" t="n">
-        <v>13.3418</v>
+        <v>13.3456</v>
       </c>
     </row>
     <row r="430">
@@ -21389,10 +21389,10 @@
         <v>1.06</v>
       </c>
       <c r="I430" t="n">
-        <v>0.1876</v>
+        <v>0.1879</v>
       </c>
       <c r="J430" t="n">
-        <v>3.5644</v>
+        <v>3.5701</v>
       </c>
     </row>
     <row r="431">
@@ -21429,10 +21429,10 @@
         <v>1.05</v>
       </c>
       <c r="I431" t="n">
-        <v>0.1573</v>
+        <v>0.1576</v>
       </c>
       <c r="J431" t="n">
-        <v>2.9887</v>
+        <v>2.9944</v>
       </c>
     </row>
     <row r="432">
@@ -21866,13 +21866,13 @@
         <v>22</v>
       </c>
       <c r="H442" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="I442" t="n">
-        <v>1.098</v>
+        <v>1.1115</v>
       </c>
       <c r="J442" t="n">
-        <v>24.156</v>
+        <v>24.453</v>
       </c>
     </row>
     <row r="443">
@@ -21909,10 +21909,10 @@
         <v>1.26</v>
       </c>
       <c r="I443" t="n">
-        <v>0.6772</v>
+        <v>0.6768</v>
       </c>
       <c r="J443" t="n">
-        <v>14.8984</v>
+        <v>14.8896</v>
       </c>
     </row>
     <row r="444">
@@ -21949,10 +21949,10 @@
         <v>1.11</v>
       </c>
       <c r="I444" t="n">
-        <v>0.3413</v>
+        <v>0.341</v>
       </c>
       <c r="J444" t="n">
-        <v>7.5086</v>
+        <v>7.502</v>
       </c>
     </row>
     <row r="445">
@@ -21989,10 +21989,10 @@
         <v>1.06</v>
       </c>
       <c r="I445" t="n">
-        <v>0.2054</v>
+        <v>0.2051</v>
       </c>
       <c r="J445" t="n">
-        <v>4.5188</v>
+        <v>4.5122</v>
       </c>
     </row>
     <row r="446">
@@ -22029,10 +22029,10 @@
         <v>0.91</v>
       </c>
       <c r="I446" t="n">
-        <v>-0.3471</v>
+        <v>-0.3475</v>
       </c>
       <c r="J446" t="n">
-        <v>-7.6362</v>
+        <v>-7.645</v>
       </c>
     </row>
     <row r="447">
@@ -22469,10 +22469,10 @@
         <v>1.52</v>
       </c>
       <c r="I457" t="n">
-        <v>0.6562</v>
+        <v>0.6558</v>
       </c>
       <c r="J457" t="n">
-        <v>26.248</v>
+        <v>26.232</v>
       </c>
     </row>
     <row r="458">
@@ -22506,13 +22506,13 @@
         <v>40</v>
       </c>
       <c r="H458" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="I458" t="n">
-        <v>0.5729</v>
+        <v>0.5831</v>
       </c>
       <c r="J458" t="n">
-        <v>22.916</v>
+        <v>23.324</v>
       </c>
     </row>
     <row r="459">
@@ -22549,10 +22549,10 @@
         <v>1.06</v>
       </c>
       <c r="I459" t="n">
-        <v>0.1151</v>
+        <v>0.1149</v>
       </c>
       <c r="J459" t="n">
-        <v>4.604</v>
+        <v>4.596</v>
       </c>
     </row>
     <row r="460">
@@ -22589,10 +22589,10 @@
         <v>0.88</v>
       </c>
       <c r="I460" t="n">
-        <v>-0.1811</v>
+        <v>-0.1813</v>
       </c>
       <c r="J460" t="n">
-        <v>-7.244</v>
+        <v>-7.252</v>
       </c>
     </row>
     <row r="461">
@@ -22629,10 +22629,10 @@
         <v>0.8</v>
       </c>
       <c r="I461" t="n">
-        <v>-0.2642</v>
+        <v>-0.2644</v>
       </c>
       <c r="J461" t="n">
-        <v>-10.568</v>
+        <v>-10.576</v>
       </c>
     </row>
     <row r="462">
@@ -24066,13 +24066,13 @@
         <v>15</v>
       </c>
       <c r="H497" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="I497" t="n">
-        <v>-0.0604</v>
+        <v>-0.0737</v>
       </c>
       <c r="J497" t="n">
-        <v>-0.906</v>
+        <v>-1.1055</v>
       </c>
     </row>
     <row r="498">
@@ -24146,13 +24146,13 @@
         <v>15</v>
       </c>
       <c r="H499" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="I499" t="n">
-        <v>-0.3651</v>
+        <v>-0.3566</v>
       </c>
       <c r="J499" t="n">
-        <v>-5.4765</v>
+        <v>-5.349</v>
       </c>
     </row>
     <row r="500">
@@ -25869,10 +25869,10 @@
         <v>1.94</v>
       </c>
       <c r="I542" t="n">
-        <v>1.6142</v>
+        <v>1.6146</v>
       </c>
       <c r="J542" t="n">
-        <v>29.0556</v>
+        <v>29.0628</v>
       </c>
     </row>
     <row r="543">
@@ -25906,13 +25906,13 @@
         <v>18</v>
       </c>
       <c r="H543" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I543" t="n">
-        <v>1.5904</v>
+        <v>1.5789</v>
       </c>
       <c r="J543" t="n">
-        <v>28.6272</v>
+        <v>28.4202</v>
       </c>
     </row>
     <row r="544">
@@ -25949,10 +25949,10 @@
         <v>1.37</v>
       </c>
       <c r="I544" t="n">
-        <v>0.8597</v>
+        <v>0.8599</v>
       </c>
       <c r="J544" t="n">
-        <v>15.4746</v>
+        <v>15.4782</v>
       </c>
     </row>
     <row r="545">
@@ -25989,10 +25989,10 @@
         <v>0.96</v>
       </c>
       <c r="I545" t="n">
-        <v>-0.2408</v>
+        <v>-0.2405</v>
       </c>
       <c r="J545" t="n">
-        <v>-4.3344</v>
+        <v>-4.329</v>
       </c>
     </row>
     <row r="546">
@@ -26029,10 +26029,10 @@
         <v>0.92</v>
       </c>
       <c r="I546" t="n">
-        <v>-0.3604</v>
+        <v>-0.3602</v>
       </c>
       <c r="J546" t="n">
-        <v>-6.4872</v>
+        <v>-6.4836</v>
       </c>
     </row>
     <row r="547">
@@ -26266,13 +26266,13 @@
         <v>18</v>
       </c>
       <c r="H552" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="I552" t="n">
-        <v>0.9987</v>
+        <v>1.0129</v>
       </c>
       <c r="J552" t="n">
-        <v>17.9766</v>
+        <v>18.2322</v>
       </c>
     </row>
     <row r="553">
@@ -26309,10 +26309,10 @@
         <v>1.88</v>
       </c>
       <c r="I553" t="n">
-        <v>0.9351</v>
+        <v>0.9346</v>
       </c>
       <c r="J553" t="n">
-        <v>16.8318</v>
+        <v>16.8228</v>
       </c>
     </row>
     <row r="554">
@@ -26349,10 +26349,10 @@
         <v>1.48</v>
       </c>
       <c r="I554" t="n">
-        <v>0.5743</v>
+        <v>0.5741000000000001</v>
       </c>
       <c r="J554" t="n">
-        <v>10.3374</v>
+        <v>10.3338</v>
       </c>
     </row>
     <row r="555">
@@ -26389,10 +26389,10 @@
         <v>1.24</v>
       </c>
       <c r="I555" t="n">
-        <v>0.3214</v>
+        <v>0.3211</v>
       </c>
       <c r="J555" t="n">
-        <v>5.7852</v>
+        <v>5.7798</v>
       </c>
     </row>
     <row r="556">
@@ -26429,10 +26429,10 @@
         <v>1.08</v>
       </c>
       <c r="I556" t="n">
-        <v>0.1131</v>
+        <v>0.1128</v>
       </c>
       <c r="J556" t="n">
-        <v>2.0358</v>
+        <v>2.0304</v>
       </c>
     </row>
     <row r="557">
@@ -26469,10 +26469,10 @@
         <v>1</v>
       </c>
       <c r="I557" t="n">
-        <v>0.0439</v>
+        <v>0.0445</v>
       </c>
       <c r="J557" t="n">
-        <v>0.7902</v>
+        <v>0.801</v>
       </c>
     </row>
     <row r="558">
@@ -26509,16 +26509,16 @@
         <v>0.93</v>
       </c>
       <c r="I558" t="n">
-        <v>-0.0854</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="J558" t="n">
-        <v>-1.5372</v>
+        <v>-1.53</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -26546,13 +26546,13 @@
         <v>18</v>
       </c>
       <c r="H559" t="n">
-        <v>0.73</v>
+        <v>0.72</v>
       </c>
       <c r="I559" t="n">
-        <v>-0.2956</v>
+        <v>-0.3045</v>
       </c>
       <c r="J559" t="n">
-        <v>-5.3208</v>
+        <v>-5.481</v>
       </c>
     </row>
     <row r="560">
@@ -26589,10 +26589,10 @@
         <v>0.7</v>
       </c>
       <c r="I560" t="n">
-        <v>-0.3229</v>
+        <v>-0.3227</v>
       </c>
       <c r="J560" t="n">
-        <v>-5.8122</v>
+        <v>-5.8086</v>
       </c>
     </row>
     <row r="561">
@@ -26629,10 +26629,10 @@
         <v>0.43</v>
       </c>
       <c r="I561" t="n">
-        <v>-0.5615</v>
+        <v>-0.5613</v>
       </c>
       <c r="J561" t="n">
-        <v>-10.107</v>
+        <v>-10.1034</v>
       </c>
     </row>
     <row r="562">
@@ -26669,10 +26669,10 @@
         <v>1.28</v>
       </c>
       <c r="I562" t="n">
-        <v>0.5817</v>
+        <v>0.581</v>
       </c>
       <c r="J562" t="n">
-        <v>12.2157</v>
+        <v>12.201</v>
       </c>
     </row>
     <row r="563">
@@ -26706,13 +26706,13 @@
         <v>21</v>
       </c>
       <c r="H563" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I563" t="n">
-        <v>0.5324</v>
+        <v>0.5483</v>
       </c>
       <c r="J563" t="n">
-        <v>11.1804</v>
+        <v>11.5143</v>
       </c>
     </row>
     <row r="564">
@@ -26749,10 +26749,10 @@
         <v>0.78</v>
       </c>
       <c r="I564" t="n">
-        <v>-0.267</v>
+        <v>-0.2672</v>
       </c>
       <c r="J564" t="n">
-        <v>-5.607</v>
+        <v>-5.6112</v>
       </c>
     </row>
     <row r="565">
@@ -26789,10 +26789,10 @@
         <v>0.72</v>
       </c>
       <c r="I565" t="n">
-        <v>-0.3242</v>
+        <v>-0.3244</v>
       </c>
       <c r="J565" t="n">
-        <v>-6.8082</v>
+        <v>-6.8124</v>
       </c>
     </row>
     <row r="566">
@@ -26829,10 +26829,10 @@
         <v>0.7</v>
       </c>
       <c r="I566" t="n">
-        <v>-0.3427</v>
+        <v>-0.3429</v>
       </c>
       <c r="J566" t="n">
-        <v>-7.1967</v>
+        <v>-7.2009</v>
       </c>
     </row>
     <row r="567">
@@ -26869,10 +26869,10 @@
         <v>1.31</v>
       </c>
       <c r="I567" t="n">
-        <v>0.8</v>
+        <v>0.8006</v>
       </c>
       <c r="J567" t="n">
-        <v>16.8</v>
+        <v>16.8126</v>
       </c>
     </row>
     <row r="568">
@@ -26906,19 +26906,19 @@
         <v>21</v>
       </c>
       <c r="H568" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="I568" t="n">
-        <v>0.5405</v>
+        <v>0.5181</v>
       </c>
       <c r="J568" t="n">
-        <v>11.3505</v>
+        <v>10.8801</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -26949,10 +26949,10 @@
         <v>1.15</v>
       </c>
       <c r="I569" t="n">
-        <v>0.4478</v>
+        <v>0.4482</v>
       </c>
       <c r="J569" t="n">
-        <v>9.4038</v>
+        <v>9.4122</v>
       </c>
     </row>
     <row r="570">
@@ -26989,10 +26989,10 @@
         <v>0.91</v>
       </c>
       <c r="I570" t="n">
-        <v>-0.3328</v>
+        <v>-0.3324</v>
       </c>
       <c r="J570" t="n">
-        <v>-6.9888</v>
+        <v>-6.9804</v>
       </c>
     </row>
     <row r="571">
@@ -27029,10 +27029,10 @@
         <v>0.89</v>
       </c>
       <c r="I571" t="n">
-        <v>-0.3862</v>
+        <v>-0.3858</v>
       </c>
       <c r="J571" t="n">
-        <v>-8.110200000000001</v>
+        <v>-8.101800000000001</v>
       </c>
     </row>
     <row r="572">
@@ -27398,7 +27398,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
@@ -27469,10 +27469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I582" t="n">
-        <v>-0.0563</v>
+        <v>-0.0568</v>
       </c>
       <c r="J582" t="n">
-        <v>-1.0697</v>
+        <v>-1.0792</v>
       </c>
     </row>
     <row r="583">
@@ -27506,13 +27506,13 @@
         <v>19</v>
       </c>
       <c r="H583" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I583" t="n">
-        <v>-0.2203</v>
+        <v>-0.2102</v>
       </c>
       <c r="J583" t="n">
-        <v>-4.1857</v>
+        <v>-3.9938</v>
       </c>
     </row>
     <row r="584">
@@ -27549,10 +27549,10 @@
         <v>0.67</v>
       </c>
       <c r="I584" t="n">
-        <v>-0.3424</v>
+        <v>-0.3426</v>
       </c>
       <c r="J584" t="n">
-        <v>-6.5056</v>
+        <v>-6.5094</v>
       </c>
     </row>
     <row r="585">
@@ -27589,10 +27589,10 @@
         <v>0.67</v>
       </c>
       <c r="I585" t="n">
-        <v>-0.3424</v>
+        <v>-0.3426</v>
       </c>
       <c r="J585" t="n">
-        <v>-6.5056</v>
+        <v>-6.5094</v>
       </c>
     </row>
     <row r="586">
@@ -27629,10 +27629,10 @@
         <v>0.36</v>
       </c>
       <c r="I586" t="n">
-        <v>-0.6143</v>
+        <v>-0.6145</v>
       </c>
       <c r="J586" t="n">
-        <v>-11.6717</v>
+        <v>-11.6755</v>
       </c>
     </row>
     <row r="587">
@@ -27866,13 +27866,13 @@
         <v>23</v>
       </c>
       <c r="H592" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="I592" t="n">
-        <v>0.0121</v>
+        <v>0.0561</v>
       </c>
       <c r="J592" t="n">
-        <v>0.2783</v>
+        <v>1.2903</v>
       </c>
     </row>
     <row r="593">
@@ -27909,10 +27909,10 @@
         <v>0.98</v>
       </c>
       <c r="I593" t="n">
-        <v>-0.0367</v>
+        <v>-0.0369</v>
       </c>
       <c r="J593" t="n">
-        <v>-0.8441</v>
+        <v>-0.8487</v>
       </c>
     </row>
     <row r="594">
@@ -27949,10 +27949,10 @@
         <v>0.95</v>
       </c>
       <c r="I594" t="n">
-        <v>-0.0805</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="J594" t="n">
-        <v>-1.8515</v>
+        <v>-1.8561</v>
       </c>
     </row>
     <row r="595">
@@ -27989,10 +27989,10 @@
         <v>0.85</v>
       </c>
       <c r="I595" t="n">
-        <v>-0.1937</v>
+        <v>-0.1939</v>
       </c>
       <c r="J595" t="n">
-        <v>-4.4551</v>
+        <v>-4.4597</v>
       </c>
     </row>
     <row r="596">
@@ -28029,10 +28029,10 @@
         <v>0.79</v>
       </c>
       <c r="I596" t="n">
-        <v>-0.2542</v>
+        <v>-0.2544</v>
       </c>
       <c r="J596" t="n">
-        <v>-5.8466</v>
+        <v>-5.8512</v>
       </c>
     </row>
     <row r="597">
@@ -28266,13 +28266,13 @@
         <v>28</v>
       </c>
       <c r="H602" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I602" t="n">
-        <v>0.9635</v>
+        <v>0.981</v>
       </c>
       <c r="J602" t="n">
-        <v>26.978</v>
+        <v>27.468</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.23</v>
       </c>
       <c r="I603" t="n">
-        <v>0.6322</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="J603" t="n">
-        <v>17.7016</v>
+        <v>17.6848</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>1.2</v>
       </c>
       <c r="I604" t="n">
-        <v>0.5654</v>
+        <v>0.5649</v>
       </c>
       <c r="J604" t="n">
-        <v>15.8312</v>
+        <v>15.8172</v>
       </c>
     </row>
     <row r="605">
@@ -28389,10 +28389,10 @@
         <v>0.93</v>
       </c>
       <c r="I605" t="n">
-        <v>-0.2749</v>
+        <v>-0.2753</v>
       </c>
       <c r="J605" t="n">
-        <v>-7.6972</v>
+        <v>-7.7084</v>
       </c>
     </row>
     <row r="606">
@@ -28429,10 +28429,10 @@
         <v>0.65</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.9296</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="J606" t="n">
-        <v>-26.0288</v>
+        <v>-26.0372</v>
       </c>
     </row>
     <row r="607">
@@ -28466,13 +28466,13 @@
         <v>28</v>
       </c>
       <c r="H607" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="I607" t="n">
-        <v>0.6496</v>
+        <v>0.6348</v>
       </c>
       <c r="J607" t="n">
-        <v>18.1888</v>
+        <v>17.7744</v>
       </c>
     </row>
     <row r="608">
@@ -28509,10 +28509,10 @@
         <v>1.22</v>
       </c>
       <c r="I608" t="n">
-        <v>0.4592</v>
+        <v>0.4597</v>
       </c>
       <c r="J608" t="n">
-        <v>12.8576</v>
+        <v>12.8716</v>
       </c>
     </row>
     <row r="609">
@@ -28549,10 +28549,10 @@
         <v>1.02</v>
       </c>
       <c r="I609" t="n">
-        <v>0.0704</v>
+        <v>0.0706</v>
       </c>
       <c r="J609" t="n">
-        <v>1.9712</v>
+        <v>1.9768</v>
       </c>
     </row>
     <row r="610">
@@ -28589,10 +28589,10 @@
         <v>0.91</v>
       </c>
       <c r="I610" t="n">
-        <v>-0.1385</v>
+        <v>-0.1383</v>
       </c>
       <c r="J610" t="n">
-        <v>-3.878</v>
+        <v>-3.8724</v>
       </c>
     </row>
     <row r="611">
@@ -28629,10 +28629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I611" t="n">
-        <v>-0.3599</v>
+        <v>-0.3598</v>
       </c>
       <c r="J611" t="n">
-        <v>-10.0772</v>
+        <v>-10.0744</v>
       </c>
     </row>
     <row r="612">
@@ -29066,13 +29066,13 @@
         <v>42</v>
       </c>
       <c r="H622" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="I622" t="n">
-        <v>1.1064</v>
+        <v>1.0928</v>
       </c>
       <c r="J622" t="n">
-        <v>46.4688</v>
+        <v>45.8976</v>
       </c>
     </row>
     <row r="623">
@@ -29109,10 +29109,10 @@
         <v>1.39</v>
       </c>
       <c r="I623" t="n">
-        <v>0.9478</v>
+        <v>0.9484</v>
       </c>
       <c r="J623" t="n">
-        <v>39.8076</v>
+        <v>39.8328</v>
       </c>
     </row>
     <row r="624">
@@ -29149,10 +29149,10 @@
         <v>1.01</v>
       </c>
       <c r="I624" t="n">
-        <v>0.0383</v>
+        <v>0.0387</v>
       </c>
       <c r="J624" t="n">
-        <v>1.6086</v>
+        <v>1.6254</v>
       </c>
     </row>
     <row r="625">
@@ -29189,10 +29189,10 @@
         <v>0.96</v>
       </c>
       <c r="I625" t="n">
-        <v>-0.193</v>
+        <v>-0.1927</v>
       </c>
       <c r="J625" t="n">
-        <v>-8.106</v>
+        <v>-8.093400000000001</v>
       </c>
     </row>
     <row r="626">
@@ -29229,10 +29229,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I626" t="n">
-        <v>-0.5903</v>
+        <v>-0.59</v>
       </c>
       <c r="J626" t="n">
-        <v>-24.7926</v>
+        <v>-24.78</v>
       </c>
     </row>
     <row r="627">
@@ -29269,10 +29269,10 @@
         <v>1.13</v>
       </c>
       <c r="I627" t="n">
-        <v>0.3034</v>
+        <v>0.303</v>
       </c>
       <c r="J627" t="n">
-        <v>12.7428</v>
+        <v>12.726</v>
       </c>
     </row>
     <row r="628">
@@ -29309,10 +29309,10 @@
         <v>1.13</v>
       </c>
       <c r="I628" t="n">
-        <v>0.3034</v>
+        <v>0.303</v>
       </c>
       <c r="J628" t="n">
-        <v>12.7428</v>
+        <v>12.726</v>
       </c>
     </row>
     <row r="629">
@@ -29346,13 +29346,13 @@
         <v>42</v>
       </c>
       <c r="H629" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I629" t="n">
-        <v>0.2849</v>
+        <v>0.303</v>
       </c>
       <c r="J629" t="n">
-        <v>11.9658</v>
+        <v>12.726</v>
       </c>
     </row>
     <row r="630">
@@ -29389,10 +29389,10 @@
         <v>0.95</v>
       </c>
       <c r="I630" t="n">
-        <v>-0.0887</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="J630" t="n">
-        <v>-3.7254</v>
+        <v>-3.7338</v>
       </c>
     </row>
     <row r="631">
@@ -29429,10 +29429,10 @@
         <v>0.84</v>
       </c>
       <c r="I631" t="n">
-        <v>-0.2149</v>
+        <v>-0.2151</v>
       </c>
       <c r="J631" t="n">
-        <v>-9.0258</v>
+        <v>-9.0342</v>
       </c>
     </row>
     <row r="632">
@@ -29718,7 +29718,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>fear</t>
+          <t>fEAR</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -29918,7 +29918,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -30909,10 +30909,10 @@
         <v>2.16</v>
       </c>
       <c r="I668" t="n">
-        <v>1.8436</v>
+        <v>1.8444</v>
       </c>
       <c r="J668" t="n">
-        <v>27.654</v>
+        <v>27.666</v>
       </c>
     </row>
     <row r="669">
@@ -30946,13 +30946,13 @@
         <v>15</v>
       </c>
       <c r="H669" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="I669" t="n">
-        <v>0.4531</v>
+        <v>0.4307</v>
       </c>
       <c r="J669" t="n">
-        <v>6.7965</v>
+        <v>6.4605</v>
       </c>
     </row>
     <row r="670">
@@ -30986,13 +30986,13 @@
         <v>15</v>
       </c>
       <c r="H670" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="I670" t="n">
-        <v>0.2588</v>
+        <v>0.2328</v>
       </c>
       <c r="J670" t="n">
-        <v>3.882</v>
+        <v>3.492</v>
       </c>
     </row>
     <row r="671">
@@ -31029,10 +31029,10 @@
         <v>0.6</v>
       </c>
       <c r="I671" t="n">
-        <v>-1.0876</v>
+        <v>-1.0873</v>
       </c>
       <c r="J671" t="n">
-        <v>-16.314</v>
+        <v>-16.3095</v>
       </c>
     </row>
     <row r="672">
